--- a/Thesis_GPR_Event_Audit_FINAL_VERIFIED.xlsx
+++ b/Thesis_GPR_Event_Audit_FINAL_VERIFIED.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c17c87fde5f3bec7/Documents/Thesis/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c17c87fde5f3bec7/Documents/GitHub/Geopolitical-Risk-Bitcoin-SA-Markets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EEF02280-0746-438F-A045-85E8649E16AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{45D65145-B999-44CC-9672-F43A4BEB76B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1805" uniqueCount="497">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3374" uniqueCount="664">
   <si>
     <t>Measure</t>
   </si>
@@ -1490,9 +1490,6 @@
     <t>Episode matching</t>
   </si>
   <si>
-    <t>After the news audit is verified, compare the identified raw-event peaks across smoothing windows. A raw event peak that appears in multiple selected windows can link those windows to the same broader Episode.</t>
-  </si>
-  <si>
     <t>Regression window</t>
   </si>
   <si>
@@ -1515,6 +1512,510 @@
   </si>
   <si>
     <t>This is a thesis write-up issue, not a table column: 11-day event regressions have only 11 observations and their Newey-West inference should be treated cautiously/descriptively.</t>
+  </si>
+  <si>
+    <t>Other_Event_IDs_Within_Window</t>
+  </si>
+  <si>
+    <t>Shared_Highest_Raw_Day_Event_IDs</t>
+  </si>
+  <si>
+    <t>Episode_Link_Status</t>
+  </si>
+  <si>
+    <t>Other_Selected_Raw_Peak_IDs_Within_Window</t>
+  </si>
+  <si>
+    <t>Additional_Event_Codes</t>
+  </si>
+  <si>
+    <t>Additional_Event_Names</t>
+  </si>
+  <si>
+    <t>Combined_Event_Codes</t>
+  </si>
+  <si>
+    <t>Combined_Event_Names</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>No overlap</t>
+  </si>
+  <si>
+    <t>GPRD_21_1; GPRD_ACT_11_1; GPRD_ACT_21_1; GPRD_THREAT_21_3</t>
+  </si>
+  <si>
+    <t>Same episode as GPRD_21_1; GPRD_ACT_11_1; GPRD_ACT_21_1; GPRD_THREAT_21_3</t>
+  </si>
+  <si>
+    <t>GPRD_21_1 (Rank 1); GPRD_ACT_11_1 (Rank 1); GPRD_ACT_21_1 (Rank 1); GPRD_THREAT_21_3 (Rank 1); GPRD_21_1 (Rank 2); GPRD_ACT_11_1 (Rank 2); GPRD_ACT_21_1 (Rank 2); GPRD_THREAT_21_3 (Rank 2); GPRD_21_1 (Rank 3); GPRD_ACT_11_1 (Rank 3); GPRD_ACT_21_1 (Rank 3); GPRD_THREAT_21_3 (Rank 3)</t>
+  </si>
+  <si>
+    <t>2015 - Paris attacks / French anti-terror response; 2015 - Russia-Turkey confrontation after Russian jet downing</t>
+  </si>
+  <si>
+    <t>GPRD_31_1; GPRD_31_2; GPRD_ACT_11_3; GPRD_THREAT_11_3</t>
+  </si>
+  <si>
+    <t>Same episode as GPRD_31_2</t>
+  </si>
+  <si>
+    <t>GPRD_31_1 (Rank 2); GPRD_ACT_11_3 (Rank 1); GPRD_31_1 (Rank 3); GPRD_ACT_11_3 (Rank 3); GPRD_THREAT_11_3 (Rank 3); GPRD_ACT_11_3 (Rank 2); GPRD_31_2 (Rank 2); GPRD_THREAT_11_3 (Rank 1); GPRD_31_2 (Rank 1); GPRD_THREAT_11_3 (Rank 2)</t>
+  </si>
+  <si>
+    <t>E25; E24</t>
+  </si>
+  <si>
+    <t>2021 - Gaza ceasefire / reconstruction aftermath; 2021 - Israel-Gaza fighting</t>
+  </si>
+  <si>
+    <t>GPRD_ACT_11_4; GPRD_ACT_21_4</t>
+  </si>
+  <si>
+    <t>Overlapping windows</t>
+  </si>
+  <si>
+    <t>GPRD_ACT_11_4 (Rank 3); GPRD_ACT_21_4 (Rank 2); GPRD_ACT_11_4 (Rank 1); GPRD_ACT_11_4 (Rank 2)</t>
+  </si>
+  <si>
+    <t>E31; E30</t>
+  </si>
+  <si>
+    <t>2025 - Russia-Ukraine ceasefire negotiations / Putin response; 2025 - US suspension of military/intelligence support to Ukraine</t>
+  </si>
+  <si>
+    <t>GPRD_21_5; GPRD_31_5; GPRD_ACT_21_5; GPRD_ACT_31_5</t>
+  </si>
+  <si>
+    <t>GPRD_21_5; GPRD_31_5</t>
+  </si>
+  <si>
+    <t>Same episode as GPRD_21_5; GPRD_31_5</t>
+  </si>
+  <si>
+    <t>GPRD_21_5 (Rank 1); GPRD_31_5 (Rank 1); GPRD_ACT_21_5 (Rank 2); GPRD_ACT_31_5 (Rank 2); GPRD_21_5 (Rank 3); GPRD_21_5 (Rank 2); GPRD_31_5 (Rank 2); GPRD_ACT_21_5 (Rank 1); GPRD_ACT_31_5 (Rank 1)</t>
+  </si>
+  <si>
+    <t>GPRD_11_2; GPRD_ACT_11_1; GPRD_ACT_21_1; GPRD_ACT_31_2; GPRD_THREAT_21_3</t>
+  </si>
+  <si>
+    <t>GPRD_11_2; GPRD_ACT_11_1; GPRD_ACT_21_1; GPRD_THREAT_21_3</t>
+  </si>
+  <si>
+    <t>Same episode as GPRD_11_2; GPRD_ACT_11_1; GPRD_ACT_21_1; GPRD_THREAT_21_3</t>
+  </si>
+  <si>
+    <t>GPRD_11_2 (Rank 1); GPRD_ACT_11_1 (Rank 1); GPRD_ACT_21_1 (Rank 1); GPRD_THREAT_21_3 (Rank 1); GPRD_11_2 (Rank 2); GPRD_ACT_11_1 (Rank 2); GPRD_ACT_21_1 (Rank 2); GPRD_THREAT_21_3 (Rank 2); GPRD_11_2 (Rank 3); GPRD_ACT_11_1 (Rank 3); GPRD_ACT_21_1 (Rank 3); GPRD_THREAT_21_3 (Rank 3); GPRD_ACT_31_2 (Rank 3); GPRD_ACT_31_2 (Rank 2); GPRD_ACT_31_2 (Rank 1)</t>
+  </si>
+  <si>
+    <t>2015 - Anti-ISIS military intervention in Syria/Iraq; 2015 - Turkey-PKK military escalation</t>
+  </si>
+  <si>
+    <t>E07; E08; E09; E10</t>
+  </si>
+  <si>
+    <t>2015 - Paris attacks / French anti-terror response; 2015 - Russia-Turkey confrontation after Russian jet downing; 2015 - Anti-ISIS military intervention in Syria/Iraq; 2015 - Turkey-PKK military escalation</t>
+  </si>
+  <si>
+    <t>GPRD_ACT_21_3 (Rank 3); GPRD_ACT_21_3 (Rank 1); GPRD_ACT_21_3 (Rank 2)</t>
+  </si>
+  <si>
+    <t>E16; E15</t>
+  </si>
+  <si>
+    <t>2017 - Tehran terrorist attacks; 2017 - Qatar diplomatic crisis / blockade</t>
+  </si>
+  <si>
+    <t>GPRD_THREAT_21_4 (Rank 2); GPRD_THREAT_21_4 (Rank 1); GPRD_THREAT_21_4 (Rank 3)</t>
+  </si>
+  <si>
+    <t>2019 - Saudi-Iran tensions following Aramco attacks; 2019 - Turkey-Syria cross-border offensive</t>
+  </si>
+  <si>
+    <t>GPRD_11_5; GPRD_31_5; GPRD_ACT_21_5; GPRD_ACT_31_5; GPRD_THREAT_31_5</t>
+  </si>
+  <si>
+    <t>GPRD_11_5; GPRD_31_5</t>
+  </si>
+  <si>
+    <t>Same episode as GPRD_11_5; GPRD_31_5</t>
+  </si>
+  <si>
+    <t>GPRD_11_5 (Rank 1); GPRD_31_5 (Rank 1); GPRD_ACT_21_5 (Rank 2); GPRD_ACT_31_5 (Rank 2); GPRD_11_5 (Rank 3); GPRD_11_5 (Rank 2); GPRD_31_5 (Rank 2); GPRD_ACT_21_5 (Rank 1); GPRD_ACT_31_5 (Rank 1); GPRD_ACT_21_5 (Rank 3); GPRD_THREAT_31_5 (Rank 2)</t>
+  </si>
+  <si>
+    <t>E34; E35</t>
+  </si>
+  <si>
+    <t>2026 - Iran war / Strait of Hormuz and energy disruption; 2026 - Iran war / US-Iran negotiations / Strait of Hormuz</t>
+  </si>
+  <si>
+    <t>GPRD_ACT_11_3 (Rank 1); GPRD_ACT_11_3 (Rank 3)</t>
+  </si>
+  <si>
+    <t>2021 - Sheikh Jarrah / Jerusalem tensions; 2021 - Israel-Gaza fighting</t>
+  </si>
+  <si>
+    <t>GPRD_11_3; GPRD_ACT_11_3; GPRD_THREAT_11_3</t>
+  </si>
+  <si>
+    <t>Same episode as GPRD_11_3</t>
+  </si>
+  <si>
+    <t>GPRD_ACT_11_3 (Rank 3); GPRD_THREAT_11_3 (Rank 3); GPRD_11_3 (Rank 3); GPRD_ACT_11_3 (Rank 2); GPRD_11_3 (Rank 2); GPRD_THREAT_11_3 (Rank 1); GPRD_11_3 (Rank 1); GPRD_THREAT_11_3 (Rank 2)</t>
+  </si>
+  <si>
+    <t>GPRD_THREAT_31_4 (Rank 3); GPRD_THREAT_31_4 (Rank 2)</t>
+  </si>
+  <si>
+    <t>GPRD_11_5; GPRD_21_5; GPRD_ACT_21_5; GPRD_ACT_31_5; GPRD_THREAT_21_5; GPRD_THREAT_31_5</t>
+  </si>
+  <si>
+    <t>GPRD_11_5; GPRD_21_5</t>
+  </si>
+  <si>
+    <t>Same episode as GPRD_11_5; GPRD_21_5</t>
+  </si>
+  <si>
+    <t>GPRD_11_5 (Rank 1); GPRD_21_5 (Rank 1); GPRD_ACT_21_5 (Rank 2); GPRD_ACT_31_5 (Rank 2); GPRD_11_5 (Rank 3); GPRD_21_5 (Rank 3); GPRD_11_5 (Rank 2); GPRD_21_5 (Rank 2); GPRD_ACT_21_5 (Rank 1); GPRD_ACT_31_5 (Rank 1); GPRD_ACT_21_5 (Rank 3); GPRD_THREAT_31_5 (Rank 2); GPRD_THREAT_31_5 (Rank 1); GPRD_THREAT_31_5 (Rank 3); GPRD_THREAT_21_5 (Rank 3); GPRD_ACT_31_5 (Rank 3); GPRD_THREAT_21_5 (Rank 1); GPRD_THREAT_21_5 (Rank 2)</t>
+  </si>
+  <si>
+    <t>E34; E36; E35</t>
+  </si>
+  <si>
+    <t>2026 - Iran war / Strait of Hormuz and energy disruption; 2026 - Iran war / Gulf shipping and Strait of Hormuz; 2026 - Iran war / US-Iran negotiations / Strait of Hormuz</t>
+  </si>
+  <si>
+    <t>GPRD_11_2; GPRD_21_1; GPRD_ACT_21_1; GPRD_THREAT_21_3</t>
+  </si>
+  <si>
+    <t>Same episode as GPRD_11_2; GPRD_21_1; GPRD_ACT_21_1; GPRD_THREAT_21_3</t>
+  </si>
+  <si>
+    <t>GPRD_11_2 (Rank 1); GPRD_21_1 (Rank 1); GPRD_ACT_21_1 (Rank 1); GPRD_THREAT_21_3 (Rank 1); GPRD_11_2 (Rank 2); GPRD_21_1 (Rank 2); GPRD_ACT_21_1 (Rank 2); GPRD_THREAT_21_3 (Rank 2); GPRD_11_2 (Rank 3); GPRD_21_1 (Rank 3); GPRD_ACT_21_1 (Rank 3); GPRD_THREAT_21_3 (Rank 3)</t>
+  </si>
+  <si>
+    <t>GPRD_THREAT_11_2 (Rank 3); GPRD_THREAT_11_2 (Rank 1); GPRD_THREAT_11_2 (Rank 2)</t>
+  </si>
+  <si>
+    <t>E22; E21</t>
+  </si>
+  <si>
+    <t>2020 - Ukrainian airliner downing / US-Iran aftermath; 2020 - US-Iran confrontation after Soleimani killing</t>
+  </si>
+  <si>
+    <t>GPRD_11_3; GPRD_31_1; GPRD_31_2; GPRD_THREAT_11_3</t>
+  </si>
+  <si>
+    <t>GPRD_31_1 (Rank 2); GPRD_31_1 (Rank 3); GPRD_THREAT_11_3 (Rank 3); GPRD_11_3 (Rank 3); GPRD_11_3 (Rank 2); GPRD_31_2 (Rank 2); GPRD_THREAT_11_3 (Rank 1); GPRD_11_3 (Rank 1); GPRD_31_2 (Rank 1); GPRD_THREAT_11_3 (Rank 2)</t>
+  </si>
+  <si>
+    <t>2021 - Israel-Gaza fighting; 2021 - Gaza ceasefire / reconstruction aftermath</t>
+  </si>
+  <si>
+    <t>GPRD_11_4; GPRD_ACT_21_4</t>
+  </si>
+  <si>
+    <t>GPRD_ACT_21_4 (Rank 2); GPRD_11_4 (Rank 2); GPRD_11_4 (Rank 1)</t>
+  </si>
+  <si>
+    <t>GPRD_THREAT_11_5 (Rank 1); GPRD_THREAT_11_5 (Rank 3); GPRD_THREAT_11_5 (Rank 2)</t>
+  </si>
+  <si>
+    <t>GPRD_11_2; GPRD_21_1; GPRD_ACT_11_1; GPRD_ACT_31_2; GPRD_THREAT_11_1; GPRD_THREAT_21_3</t>
+  </si>
+  <si>
+    <t>GPRD_11_2; GPRD_21_1; GPRD_ACT_11_1; GPRD_THREAT_21_3</t>
+  </si>
+  <si>
+    <t>Same episode as GPRD_11_2; GPRD_21_1; GPRD_ACT_11_1; GPRD_THREAT_21_3</t>
+  </si>
+  <si>
+    <t>GPRD_11_2 (Rank 1); GPRD_21_1 (Rank 1); GPRD_ACT_11_1 (Rank 1); GPRD_THREAT_21_3 (Rank 1); GPRD_11_2 (Rank 2); GPRD_21_1 (Rank 2); GPRD_ACT_11_1 (Rank 2); GPRD_THREAT_21_3 (Rank 2); GPRD_11_2 (Rank 3); GPRD_21_1 (Rank 3); GPRD_ACT_11_1 (Rank 3); GPRD_THREAT_21_3 (Rank 3); GPRD_ACT_31_2 (Rank 3); GPRD_ACT_31_2 (Rank 2); GPRD_ACT_31_2 (Rank 1); GPRD_THREAT_11_1 (Rank 1)</t>
+  </si>
+  <si>
+    <t>E09; E10; E11</t>
+  </si>
+  <si>
+    <t>2015 - Anti-ISIS military intervention in Syria/Iraq; 2015 - Turkey-PKK military escalation; 2016 - North Korea nuclear test</t>
+  </si>
+  <si>
+    <t>E07; E08; E09; E10; E11</t>
+  </si>
+  <si>
+    <t>2015 - Paris attacks / French anti-terror response; 2015 - Russia-Turkey confrontation after Russian jet downing; 2015 - Anti-ISIS military intervention in Syria/Iraq; 2015 - Turkey-PKK military escalation; 2016 - North Korea nuclear test</t>
+  </si>
+  <si>
+    <t>GPRD_21_2 (Rank 3); GPRD_21_2 (Rank 2); GPRD_21_2 (Rank 1)</t>
+  </si>
+  <si>
+    <t>2017 - Qatar diplomatic crisis / blockade; 2017 - Tehran terrorist attacks</t>
+  </si>
+  <si>
+    <t>GPRD_11_4 (Rank 3); GPRD_ACT_11_4 (Rank 3); GPRD_11_4 (Rank 2)</t>
+  </si>
+  <si>
+    <t>GPRD_11_5; GPRD_21_5; GPRD_31_5; GPRD_ACT_31_5; GPRD_THREAT_31_5</t>
+  </si>
+  <si>
+    <t>Same episode as GPRD_ACT_31_5</t>
+  </si>
+  <si>
+    <t>GPRD_11_5 (Rank 1); GPRD_21_5 (Rank 1); GPRD_31_5 (Rank 1); GPRD_ACT_31_5 (Rank 2); GPRD_11_5 (Rank 3); GPRD_21_5 (Rank 3); GPRD_11_5 (Rank 2); GPRD_21_5 (Rank 2); GPRD_31_5 (Rank 2); GPRD_ACT_31_5 (Rank 1); GPRD_THREAT_31_5 (Rank 2)</t>
+  </si>
+  <si>
+    <t>E10; E09</t>
+  </si>
+  <si>
+    <t>2015 - Turkey-PKK military escalation; 2015 - Anti-ISIS military intervention in Syria/Iraq</t>
+  </si>
+  <si>
+    <t>2017 - Israel-Syria military confrontation near Damascus; 2017 - Islamic State offensive around Deir ez-Zor</t>
+  </si>
+  <si>
+    <t>GPRD_11_5; GPRD_21_5; GPRD_31_5; GPRD_ACT_21_5; GPRD_THREAT_21_5; GPRD_THREAT_31_5</t>
+  </si>
+  <si>
+    <t>Same episode as GPRD_ACT_21_5</t>
+  </si>
+  <si>
+    <t>GPRD_11_5 (Rank 1); GPRD_21_5 (Rank 1); GPRD_31_5 (Rank 1); GPRD_ACT_21_5 (Rank 2); GPRD_11_5 (Rank 3); GPRD_21_5 (Rank 3); GPRD_11_5 (Rank 2); GPRD_21_5 (Rank 2); GPRD_31_5 (Rank 2); GPRD_ACT_21_5 (Rank 1); GPRD_ACT_21_5 (Rank 3); GPRD_THREAT_31_5 (Rank 2); GPRD_THREAT_31_5 (Rank 1); GPRD_THREAT_31_5 (Rank 3); GPRD_THREAT_21_5 (Rank 3); GPRD_31_5 (Rank 3); GPRD_THREAT_21_5 (Rank 1); GPRD_THREAT_21_5 (Rank 2)</t>
+  </si>
+  <si>
+    <t>GPRD_ACT_11_2 (Rank 2); GPRD_ACT_11_2 (Rank 1); GPRD_ACT_11_2 (Rank 3)</t>
+  </si>
+  <si>
+    <t>2020 - US-Iran confrontation after Soleimani killing; 2020 - Ukrainian airliner downing / US-Iran aftermath</t>
+  </si>
+  <si>
+    <t>GPRD_11_3; GPRD_31_1; GPRD_31_2; GPRD_ACT_11_3</t>
+  </si>
+  <si>
+    <t>GPRD_31_1 (Rank 2); GPRD_ACT_11_3 (Rank 1); GPRD_31_1 (Rank 3); GPRD_ACT_11_3 (Rank 3); GPRD_11_3 (Rank 3); GPRD_ACT_11_3 (Rank 2); GPRD_11_3 (Rank 2); GPRD_31_2 (Rank 2); GPRD_11_3 (Rank 1); GPRD_31_2 (Rank 1)</t>
+  </si>
+  <si>
+    <t>Same episode as GPRD_THREAT_31_2</t>
+  </si>
+  <si>
+    <t>GPRD_THREAT_31_2 (Rank 2); GPRD_THREAT_31_2 (Rank 1); GPRD_THREAT_31_2 (Rank 3)</t>
+  </si>
+  <si>
+    <t>GPRD_31_4; GPRD_ACT_11_5; GPRD_THREAT_31_4</t>
+  </si>
+  <si>
+    <t>GPRD_31_4 (Rank 1); GPRD_THREAT_31_4 (Rank 2); GPRD_ACT_11_5 (Rank 2); GPRD_ACT_11_5 (Rank 1); GPRD_ACT_11_5 (Rank 3)</t>
+  </si>
+  <si>
+    <t>E33; E32</t>
+  </si>
+  <si>
+    <t>2025 - Israel-Iran war / US intervention / ceasefire; 2025 - Gaza humanitarian aid / distribution crisis</t>
+  </si>
+  <si>
+    <t>E03; E04; E02</t>
+  </si>
+  <si>
+    <t>2014 - ISIS killing of James Foley; 2014 - Israel-Gaza ceasefire collapse / renewed fighting; 2014 - Russian humanitarian aid convoy / Ukraine</t>
+  </si>
+  <si>
+    <t>GPRD_11_2; GPRD_21_1; GPRD_ACT_11_1; GPRD_ACT_21_1; GPRD_ACT_31_2</t>
+  </si>
+  <si>
+    <t>GPRD_11_2; GPRD_21_1; GPRD_ACT_11_1; GPRD_ACT_21_1</t>
+  </si>
+  <si>
+    <t>Same episode as GPRD_11_2; GPRD_21_1; GPRD_ACT_11_1; GPRD_ACT_21_1</t>
+  </si>
+  <si>
+    <t>GPRD_11_2 (Rank 1); GPRD_21_1 (Rank 1); GPRD_ACT_11_1 (Rank 1); GPRD_ACT_21_1 (Rank 1); GPRD_11_2 (Rank 2); GPRD_21_1 (Rank 2); GPRD_ACT_11_1 (Rank 2); GPRD_ACT_21_1 (Rank 2); GPRD_11_2 (Rank 3); GPRD_21_1 (Rank 3); GPRD_ACT_11_1 (Rank 3); GPRD_ACT_21_1 (Rank 3); GPRD_ACT_31_2 (Rank 3); GPRD_ACT_31_2 (Rank 2); GPRD_ACT_31_2 (Rank 1)</t>
+  </si>
+  <si>
+    <t>GPRD_21_3 (Rank 1); GPRD_21_3 (Rank 2); GPRD_21_3 (Rank 3)</t>
+  </si>
+  <si>
+    <t>GPRD_31_5; GPRD_ACT_31_5</t>
+  </si>
+  <si>
+    <t>GPRD_31_5 (Rank 3); GPRD_ACT_31_5 (Rank 3)</t>
+  </si>
+  <si>
+    <t>Same episode as GPRD_THREAT_11_4</t>
+  </si>
+  <si>
+    <t>GPRD_THREAT_11_4 (Rank 2); GPRD_THREAT_11_4 (Rank 1); GPRD_THREAT_11_4 (Rank 3)</t>
+  </si>
+  <si>
+    <t>GPRD_31_4 (Rank 2); GPRD_31_4 (Rank 3); GPRD_31_4 (Rank 1)</t>
+  </si>
+  <si>
+    <t>GPRD_THREAT_21_5 (Rank 3)</t>
+  </si>
+  <si>
+    <t>E35; E36</t>
+  </si>
+  <si>
+    <t>2026 - Iran war / US-Iran negotiations / Strait of Hormuz; 2026 - Iran war / Gulf shipping and Strait of Hormuz</t>
+  </si>
+  <si>
+    <t>Other_Event_Window_IDs</t>
+  </si>
+  <si>
+    <t>Overlap_Status</t>
+  </si>
+  <si>
+    <t>Additional_Event_Status</t>
+  </si>
+  <si>
+    <t>No new underlying event</t>
+  </si>
+  <si>
+    <t>Shared highest raw day</t>
+  </si>
+  <si>
+    <t>Other event window only</t>
+  </si>
+  <si>
+    <t>GPRD_31_2; GPRD_ACT_11_3; GPRD_THREAT_11_3</t>
+  </si>
+  <si>
+    <t>Additional event(s) identified</t>
+  </si>
+  <si>
+    <t>GPRD_11_5; GPRD_31_5; GPRD_ACT_21_5; GPRD_ACT_31_5</t>
+  </si>
+  <si>
+    <t>GPRD_THREAT_11_5; GPRD_THREAT_31_4</t>
+  </si>
+  <si>
+    <t>GPRD_11_5; GPRD_21_5; GPRD_ACT_21_5; GPRD_ACT_31_5</t>
+  </si>
+  <si>
+    <t>GPRD_ACT_31_5; GPRD_THREAT_21_5</t>
+  </si>
+  <si>
+    <t>GPRD_11_3; GPRD_31_1; GPRD_THREAT_11_3</t>
+  </si>
+  <si>
+    <t>GPRD_11_3; GPRD_31_2; GPRD_THREAT_11_3</t>
+  </si>
+  <si>
+    <t>GPRD_11_5; GPRD_21_5; GPRD_31_5; GPRD_ACT_31_5</t>
+  </si>
+  <si>
+    <t>GPRD_21_5; GPRD_31_5; GPRD_ACT_31_5</t>
+  </si>
+  <si>
+    <t>GPRD_11_5; GPRD_21_5; GPRD_31_5; GPRD_ACT_21_5</t>
+  </si>
+  <si>
+    <t>GPRD_31_5; GPRD_THREAT_21_5</t>
+  </si>
+  <si>
+    <t>GPRD_11_3; GPRD_31_2; GPRD_ACT_11_3</t>
+  </si>
+  <si>
+    <t>GPRD_31_4; GPRD_THREAT_11_5</t>
+  </si>
+  <si>
+    <t>GPRD_11_2 (Rank 1); GPRD_11_2 (Rank 2); GPRD_11_2 (Rank 3); GPRD_21_1 (Rank 1); GPRD_21_1 (Rank 2); GPRD_21_1 (Rank 3); GPRD_ACT_11_1 (Rank 1); GPRD_ACT_11_1 (Rank 2); GPRD_ACT_11_1 (Rank 3); GPRD_ACT_21_1 (Rank 1); GPRD_ACT_21_1 (Rank 2); GPRD_ACT_21_1 (Rank 3); GPRD_THREAT_21_3 (Rank 1); GPRD_THREAT_21_3 (Rank 2); GPRD_THREAT_21_3 (Rank 3)</t>
+  </si>
+  <si>
+    <t>GPRD_11_2 (Rank 1); GPRD_11_2 (Rank 2); GPRD_11_2 (Rank 3); GPRD_21_1 (Rank 1); GPRD_21_1 (Rank 2); GPRD_21_1 (Rank 3); GPRD_ACT_11_1 (Rank 1); GPRD_ACT_11_1 (Rank 2); GPRD_ACT_11_1 (Rank 3); GPRD_ACT_21_1 (Rank 1); GPRD_ACT_21_1 (Rank 2); GPRD_ACT_21_1 (Rank 3); GPRD_ACT_31_2 (Rank 1); GPRD_ACT_31_2 (Rank 2); GPRD_ACT_31_2 (Rank 3); GPRD_THREAT_11_1 (Rank 1); GPRD_THREAT_21_3 (Rank 1); GPRD_THREAT_21_3 (Rank 2); GPRD_THREAT_21_3 (Rank 3)</t>
+  </si>
+  <si>
+    <t>E07 – 2015 - Paris attacks / French anti-terror response; E08 – 2015 - Russia-Turkey confrontation after Russian jet downing; E09 – 2015 - Anti-ISIS military intervention in Syria/Iraq; E10 – 2015 - Turkey-PKK military escalation; E11 – 2016 - North Korea nuclear test</t>
+  </si>
+  <si>
+    <t>GPRD_21_2 (Rank 1); GPRD_21_2 (Rank 2); GPRD_21_2 (Rank 3); GPRD_ACT_21_3 (Rank 1); GPRD_ACT_21_3 (Rank 2); GPRD_ACT_21_3 (Rank 3)</t>
+  </si>
+  <si>
+    <t>GPRD_21_3 (Rank 1); GPRD_21_3 (Rank 2); GPRD_21_3 (Rank 3); GPRD_THREAT_21_4 (Rank 1); GPRD_THREAT_21_4 (Rank 2); GPRD_THREAT_21_4 (Rank 3)</t>
+  </si>
+  <si>
+    <t>GPRD_THREAT_11_2 (Rank 1); GPRD_THREAT_11_2 (Rank 2); GPRD_THREAT_11_2 (Rank 3)</t>
+  </si>
+  <si>
+    <t>GPRD_ACT_11_2 (Rank 1); GPRD_ACT_11_2 (Rank 2); GPRD_ACT_11_2 (Rank 3)</t>
+  </si>
+  <si>
+    <t>GPRD_31_1; GPRD_31_2; GPRD_THREAT_11_3</t>
+  </si>
+  <si>
+    <t>GPRD_11_3 (Rank 1); GPRD_11_3 (Rank 2); GPRD_11_3 (Rank 3); GPRD_31_1 (Rank 2); GPRD_31_1 (Rank 3); GPRD_31_2 (Rank 1); GPRD_31_2 (Rank 2); GPRD_ACT_11_3 (Rank 1); GPRD_ACT_11_3 (Rank 2); GPRD_ACT_11_3 (Rank 3); GPRD_THREAT_11_3 (Rank 1); GPRD_THREAT_11_3 (Rank 2); GPRD_THREAT_11_3 (Rank 3)</t>
+  </si>
+  <si>
+    <t>GPRD_11_3 (Rank 1); GPRD_11_3 (Rank 2); GPRD_11_3 (Rank 3); GPRD_31_1 (Rank 2); GPRD_31_1 (Rank 3); GPRD_31_2 (Rank 1); GPRD_31_2 (Rank 2); GPRD_ACT_11_3 (Rank 1); GPRD_ACT_11_3 (Rank 2); GPRD_ACT_11_3 (Rank 3)</t>
+  </si>
+  <si>
+    <t>GPRD_11_3 (Rank 1); GPRD_11_3 (Rank 2); GPRD_11_3 (Rank 3); GPRD_ACT_11_3 (Rank 2); GPRD_ACT_11_3 (Rank 3); GPRD_THREAT_11_3 (Rank 1); GPRD_THREAT_11_3 (Rank 2); GPRD_THREAT_11_3 (Rank 3)</t>
+  </si>
+  <si>
+    <t>E25 – 2021 - Gaza ceasefire / reconstruction aftermath; E24 – 2021 - Israel-Gaza fighting</t>
+  </si>
+  <si>
+    <t>GPRD_THREAT_31_2 (Rank 1); GPRD_THREAT_31_2 (Rank 2); GPRD_THREAT_31_2 (Rank 3)</t>
+  </si>
+  <si>
+    <t>GPRD_THREAT_11_4 (Rank 1); GPRD_THREAT_11_4 (Rank 2); GPRD_THREAT_11_4 (Rank 3)</t>
+  </si>
+  <si>
+    <t>GPRD_11_4 (Rank 2); GPRD_11_4 (Rank 3); GPRD_ACT_11_4 (Rank 3)</t>
+  </si>
+  <si>
+    <t>E31 – 2025 - Russia-Ukraine ceasefire negotiations / Putin response; E30 – 2025 - US suspension of military/intelligence support to Ukraine</t>
+  </si>
+  <si>
+    <t>GPRD_11_4 (Rank 1); GPRD_11_4 (Rank 2); GPRD_ACT_11_4 (Rank 1); GPRD_ACT_11_4 (Rank 2); GPRD_ACT_11_4 (Rank 3); GPRD_ACT_21_4 (Rank 2)</t>
+  </si>
+  <si>
+    <t>GPRD_31_4 (Rank 1); GPRD_31_4 (Rank 2); GPRD_31_4 (Rank 3); GPRD_THREAT_31_4 (Rank 2); GPRD_THREAT_31_4 (Rank 3)</t>
+  </si>
+  <si>
+    <t>GPRD_31_4 (Rank 1); GPRD_ACT_11_5 (Rank 1); GPRD_ACT_11_5 (Rank 2); GPRD_ACT_11_5 (Rank 3); GPRD_THREAT_31_4 (Rank 2)</t>
+  </si>
+  <si>
+    <t>E33 – 2025 - Israel-Iran war / US intervention / ceasefire; E32 – 2025 - Gaza humanitarian aid / distribution crisis</t>
+  </si>
+  <si>
+    <t>GPRD_THREAT_11_5 (Rank 1); GPRD_THREAT_11_5 (Rank 2); GPRD_THREAT_11_5 (Rank 3)</t>
+  </si>
+  <si>
+    <t>GPRD_21_5 (Rank 1); GPRD_21_5 (Rank 2); GPRD_21_5 (Rank 3); GPRD_31_5 (Rank 1); GPRD_31_5 (Rank 2); GPRD_ACT_21_5 (Rank 1); GPRD_ACT_21_5 (Rank 2); GPRD_ACT_31_5 (Rank 1); GPRD_ACT_31_5 (Rank 2)</t>
+  </si>
+  <si>
+    <t>GPRD_11_5; GPRD_31_5; GPRD_ACT_31_5</t>
+  </si>
+  <si>
+    <t>GPRD_11_5 (Rank 1); GPRD_11_5 (Rank 2); GPRD_11_5 (Rank 3); GPRD_21_5 (Rank 1); GPRD_21_5 (Rank 2); GPRD_21_5 (Rank 3); GPRD_31_5 (Rank 1); GPRD_31_5 (Rank 2); GPRD_ACT_21_5 (Rank 1); GPRD_ACT_21_5 (Rank 2); GPRD_ACT_21_5 (Rank 3); GPRD_ACT_31_5 (Rank 1); GPRD_ACT_31_5 (Rank 2); GPRD_THREAT_31_5 (Rank 2)</t>
+  </si>
+  <si>
+    <t>E34 – 2026 - Iran war / Strait of Hormuz and energy disruption; E35 – 2026 - Iran war / US-Iran negotiations / Strait of Hormuz</t>
+  </si>
+  <si>
+    <t>GPRD_11_5; GPRD_21_5; GPRD_ACT_21_5; GPRD_THREAT_21_5</t>
+  </si>
+  <si>
+    <t>GPRD_11_5; GPRD_21_5; GPRD_ACT_21_5</t>
+  </si>
+  <si>
+    <t>GPRD_11_5 (Rank 1); GPRD_11_5 (Rank 2); GPRD_11_5 (Rank 3); GPRD_21_5 (Rank 1); GPRD_21_5 (Rank 2); GPRD_21_5 (Rank 3); GPRD_31_5 (Rank 1); GPRD_31_5 (Rank 2); GPRD_31_5 (Rank 3); GPRD_ACT_21_5 (Rank 1); GPRD_ACT_21_5 (Rank 2); GPRD_ACT_21_5 (Rank 3); GPRD_ACT_31_5 (Rank 1); GPRD_ACT_31_5 (Rank 2); GPRD_ACT_31_5 (Rank 3); GPRD_THREAT_21_5 (Rank 1); GPRD_THREAT_21_5 (Rank 2); GPRD_THREAT_21_5 (Rank 3); GPRD_THREAT_31_5 (Rank 1); GPRD_THREAT_31_5 (Rank 2); GPRD_THREAT_31_5 (Rank 3)</t>
+  </si>
+  <si>
+    <t>Two selected peaks are treated as the same episode only if their full smoothed event windows share the same highest raw GPR day. An overlap between windows alone does not merge episodes.</t>
+  </si>
+  <si>
+    <t>Additional raw-peak overlap audit</t>
+  </si>
+  <si>
+    <t>The 135 Raw Peak Audit checks every selected raw peak against the full smoothed window of every other Event_ID. Other-event-window overlap is recorded for any raw rank. Shared highest raw days, and therefore same-episode links, are identified only from Raw_Rank 1 (the highest raw GPR observation for each Event_ID) using exact date equality. These additional flags do not change the top-three raw-peak selection or event naming.</t>
+  </si>
+  <si>
+    <t>Additional event propagation</t>
+  </si>
+  <si>
+    <t>For each Event_ID, compare its full smoothed event window with all three selected raw peak dates from every other Event_ID. If any other test's selected raw peak falls within the window, the underlying event code and event name associated with that raw peak are recorded as an additional event, provided they are not already among the current test's identified events. Existing top-three raw-peak selection and event naming are not replaced.</t>
   </si>
 </sst>
 </file>
@@ -1678,7 +2179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1733,6 +2234,9 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1946,7 +2450,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T46"/>
+  <dimension ref="A1:AB46"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -1960,10 +2464,17 @@
     <col min="12" max="12" width="14" customWidth="1"/>
     <col min="13" max="13" width="13" customWidth="1"/>
     <col min="14" max="19" width="42" customWidth="1"/>
-    <col min="20" max="20" width="38" customWidth="1"/>
+    <col min="20" max="21" width="38" customWidth="1"/>
+    <col min="22" max="22" width="34" customWidth="1"/>
+    <col min="23" max="23" width="28" customWidth="1"/>
+    <col min="24" max="24" width="38" customWidth="1"/>
+    <col min="25" max="25" width="20" customWidth="1"/>
+    <col min="26" max="26" width="48" customWidth="1"/>
+    <col min="27" max="27" width="24" customWidth="1"/>
+    <col min="28" max="28" width="58" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="19.2" customHeight="1">
+    <row r="1" spans="1:28" ht="21.15" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2024,8 +2535,32 @@
       <c r="T1" s="3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" spans="1:20" ht="27.6">
+      <c r="U1" s="19" t="s">
+        <v>496</v>
+      </c>
+      <c r="V1" s="19" t="s">
+        <v>497</v>
+      </c>
+      <c r="W1" s="19" t="s">
+        <v>498</v>
+      </c>
+      <c r="X1" s="19" t="s">
+        <v>499</v>
+      </c>
+      <c r="Y1" s="19" t="s">
+        <v>500</v>
+      </c>
+      <c r="Z1" s="19" t="s">
+        <v>501</v>
+      </c>
+      <c r="AA1" s="19" t="s">
+        <v>502</v>
+      </c>
+      <c r="AB1" s="19" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" ht="21.15" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>20</v>
       </c>
@@ -2082,8 +2617,32 @@
       <c r="T2" s="6" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="3" spans="1:20" ht="27.6">
+      <c r="U2" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="V2" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="W2" s="19" t="s">
+        <v>505</v>
+      </c>
+      <c r="X2" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Y2" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Z2" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="AA2" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="AB2" s="19" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" ht="31.65" customHeight="1">
       <c r="A3" s="7" t="s">
         <v>20</v>
       </c>
@@ -2142,8 +2701,32 @@
       <c r="T3" s="9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="4" spans="1:20" ht="27.6">
+      <c r="U3" s="19" t="s">
+        <v>506</v>
+      </c>
+      <c r="V3" s="19" t="s">
+        <v>506</v>
+      </c>
+      <c r="W3" s="19" t="s">
+        <v>507</v>
+      </c>
+      <c r="X3" s="19" t="s">
+        <v>508</v>
+      </c>
+      <c r="Y3" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Z3" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="AA3" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="AB3" s="19" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" ht="21.15" customHeight="1">
       <c r="A4" s="7" t="s">
         <v>20</v>
       </c>
@@ -2200,8 +2783,32 @@
       <c r="T4" s="9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="5" spans="1:20" ht="27.6">
+      <c r="U4" s="19" t="s">
+        <v>510</v>
+      </c>
+      <c r="V4" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="W4" s="19" t="s">
+        <v>511</v>
+      </c>
+      <c r="X4" s="19" t="s">
+        <v>512</v>
+      </c>
+      <c r="Y4" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="Z4" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="AA4" s="19" t="s">
+        <v>513</v>
+      </c>
+      <c r="AB4" s="19" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" ht="21.15" customHeight="1">
       <c r="A5" s="7" t="s">
         <v>20</v>
       </c>
@@ -2260,8 +2867,32 @@
       <c r="T5" s="9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="6" spans="1:20" ht="27.6">
+      <c r="U5" s="19" t="s">
+        <v>515</v>
+      </c>
+      <c r="V5" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="W5" s="19" t="s">
+        <v>516</v>
+      </c>
+      <c r="X5" s="19" t="s">
+        <v>517</v>
+      </c>
+      <c r="Y5" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Z5" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="AA5" s="19" t="s">
+        <v>518</v>
+      </c>
+      <c r="AB5" s="19" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" ht="21.15" customHeight="1">
       <c r="A6" s="7" t="s">
         <v>20</v>
       </c>
@@ -2318,8 +2949,32 @@
       <c r="T6" s="9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="7" spans="1:20" ht="27.6">
+      <c r="U6" s="19" t="s">
+        <v>520</v>
+      </c>
+      <c r="V6" s="19" t="s">
+        <v>521</v>
+      </c>
+      <c r="W6" s="19" t="s">
+        <v>522</v>
+      </c>
+      <c r="X6" s="19" t="s">
+        <v>523</v>
+      </c>
+      <c r="Y6" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Z6" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="AA6" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="AB6" s="19" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" ht="31.65" customHeight="1">
       <c r="A7" s="7" t="s">
         <v>20</v>
       </c>
@@ -2378,8 +3033,32 @@
       <c r="T7" s="9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" ht="27.6">
+      <c r="U7" s="19" t="s">
+        <v>524</v>
+      </c>
+      <c r="V7" s="19" t="s">
+        <v>525</v>
+      </c>
+      <c r="W7" s="19" t="s">
+        <v>526</v>
+      </c>
+      <c r="X7" s="19" t="s">
+        <v>527</v>
+      </c>
+      <c r="Y7" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="Z7" s="19" t="s">
+        <v>528</v>
+      </c>
+      <c r="AA7" s="19" t="s">
+        <v>529</v>
+      </c>
+      <c r="AB7" s="19" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" ht="21.15" customHeight="1">
       <c r="A8" s="7" t="s">
         <v>20</v>
       </c>
@@ -2438,8 +3117,32 @@
       <c r="T8" s="9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" ht="27.6">
+      <c r="U8" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="V8" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="W8" s="19" t="s">
+        <v>516</v>
+      </c>
+      <c r="X8" s="19" t="s">
+        <v>531</v>
+      </c>
+      <c r="Y8" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Z8" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="AA8" s="19" t="s">
+        <v>532</v>
+      </c>
+      <c r="AB8" s="19" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" ht="21.15" customHeight="1">
       <c r="A9" s="7" t="s">
         <v>20</v>
       </c>
@@ -2498,8 +3201,32 @@
       <c r="T9" s="9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" ht="27.6">
+      <c r="U9" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="V9" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="W9" s="19" t="s">
+        <v>516</v>
+      </c>
+      <c r="X9" s="19" t="s">
+        <v>534</v>
+      </c>
+      <c r="Y9" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Z9" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="AA9" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="AB9" s="19" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" ht="21.15" customHeight="1">
       <c r="A10" s="7" t="s">
         <v>20</v>
       </c>
@@ -2556,8 +3283,32 @@
       <c r="T10" s="9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" ht="27.6">
+      <c r="U10" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="V10" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="W10" s="19" t="s">
+        <v>505</v>
+      </c>
+      <c r="X10" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Y10" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Z10" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="AA10" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="AB10" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" ht="21.15" customHeight="1">
       <c r="A11" s="7" t="s">
         <v>20</v>
       </c>
@@ -2614,8 +3365,32 @@
       <c r="T11" s="9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="12" spans="1:20" ht="27.6">
+      <c r="U11" s="19" t="s">
+        <v>536</v>
+      </c>
+      <c r="V11" s="19" t="s">
+        <v>537</v>
+      </c>
+      <c r="W11" s="19" t="s">
+        <v>538</v>
+      </c>
+      <c r="X11" s="19" t="s">
+        <v>539</v>
+      </c>
+      <c r="Y11" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="Z11" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA11" s="19" t="s">
+        <v>540</v>
+      </c>
+      <c r="AB11" s="19" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" ht="21.15" customHeight="1">
       <c r="A12" s="7" t="s">
         <v>20</v>
       </c>
@@ -2674,8 +3449,32 @@
       <c r="T12" s="9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" ht="27.6">
+      <c r="U12" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="V12" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="W12" s="19" t="s">
+        <v>516</v>
+      </c>
+      <c r="X12" s="19" t="s">
+        <v>542</v>
+      </c>
+      <c r="Y12" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Z12" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="AA12" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="AB12" s="19" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" ht="21.15" customHeight="1">
       <c r="A13" s="7" t="s">
         <v>20</v>
       </c>
@@ -2732,8 +3531,32 @@
       <c r="T13" s="9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" ht="27.6">
+      <c r="U13" s="19" t="s">
+        <v>544</v>
+      </c>
+      <c r="V13" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="W13" s="19" t="s">
+        <v>545</v>
+      </c>
+      <c r="X13" s="19" t="s">
+        <v>546</v>
+      </c>
+      <c r="Y13" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="Z13" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="AA13" s="19" t="s">
+        <v>513</v>
+      </c>
+      <c r="AB13" s="19" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" ht="21.15" customHeight="1">
       <c r="A14" s="7" t="s">
         <v>20</v>
       </c>
@@ -2790,8 +3613,32 @@
       <c r="T14" s="9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" ht="27.6">
+      <c r="U14" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="V14" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="W14" s="19" t="s">
+        <v>505</v>
+      </c>
+      <c r="X14" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Y14" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Z14" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="AA14" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="AB14" s="19" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" ht="21.15" customHeight="1">
       <c r="A15" s="7" t="s">
         <v>20</v>
       </c>
@@ -2848,8 +3695,32 @@
       <c r="T15" s="9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" ht="27.6">
+      <c r="U15" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="V15" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="W15" s="19" t="s">
+        <v>516</v>
+      </c>
+      <c r="X15" s="19" t="s">
+        <v>547</v>
+      </c>
+      <c r="Y15" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Z15" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="AA15" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="AB15" s="19" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" ht="31.65" customHeight="1">
       <c r="A16" s="7" t="s">
         <v>20</v>
       </c>
@@ -2908,8 +3779,32 @@
       <c r="T16" s="9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="17" spans="1:20" ht="27.6">
+      <c r="U16" s="19" t="s">
+        <v>548</v>
+      </c>
+      <c r="V16" s="19" t="s">
+        <v>549</v>
+      </c>
+      <c r="W16" s="19" t="s">
+        <v>550</v>
+      </c>
+      <c r="X16" s="19" t="s">
+        <v>551</v>
+      </c>
+      <c r="Y16" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="Z16" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA16" s="19" t="s">
+        <v>552</v>
+      </c>
+      <c r="AB16" s="19" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="17" spans="1:28" ht="31.65" customHeight="1">
       <c r="A17" s="7" t="s">
         <v>54</v>
       </c>
@@ -2968,8 +3863,32 @@
       <c r="T17" s="9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="18" spans="1:20" ht="27.6">
+      <c r="U17" s="19" t="s">
+        <v>554</v>
+      </c>
+      <c r="V17" s="19" t="s">
+        <v>554</v>
+      </c>
+      <c r="W17" s="19" t="s">
+        <v>555</v>
+      </c>
+      <c r="X17" s="19" t="s">
+        <v>556</v>
+      </c>
+      <c r="Y17" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Z17" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="AA17" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="AB17" s="19" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="18" spans="1:28" ht="21.15" customHeight="1">
       <c r="A18" s="7" t="s">
         <v>54</v>
       </c>
@@ -3028,8 +3947,32 @@
       <c r="T18" s="9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="19" spans="1:20" ht="27.6">
+      <c r="U18" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="V18" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="W18" s="19" t="s">
+        <v>516</v>
+      </c>
+      <c r="X18" s="19" t="s">
+        <v>557</v>
+      </c>
+      <c r="Y18" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Z18" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="AA18" s="19" t="s">
+        <v>558</v>
+      </c>
+      <c r="AB18" s="19" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="19" spans="1:28" ht="21.15" customHeight="1">
       <c r="A19" s="7" t="s">
         <v>54</v>
       </c>
@@ -3088,8 +4031,32 @@
       <c r="T19" s="9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="20" spans="1:20" ht="27.6">
+      <c r="U19" s="19" t="s">
+        <v>560</v>
+      </c>
+      <c r="V19" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="W19" s="19" t="s">
+        <v>516</v>
+      </c>
+      <c r="X19" s="19" t="s">
+        <v>561</v>
+      </c>
+      <c r="Y19" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Z19" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="AA19" s="19" t="s">
+        <v>203</v>
+      </c>
+      <c r="AB19" s="19" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="20" spans="1:28" ht="21.15" customHeight="1">
       <c r="A20" s="7" t="s">
         <v>54</v>
       </c>
@@ -3146,8 +4113,32 @@
       <c r="T20" s="9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="21" spans="1:20" ht="27.6">
+      <c r="U20" s="19" t="s">
+        <v>563</v>
+      </c>
+      <c r="V20" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="W20" s="19" t="s">
+        <v>516</v>
+      </c>
+      <c r="X20" s="19" t="s">
+        <v>564</v>
+      </c>
+      <c r="Y20" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Z20" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="AA20" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="AB20" s="19" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:28" ht="21.15" customHeight="1">
       <c r="A21" s="7" t="s">
         <v>54</v>
       </c>
@@ -3204,8 +4195,32 @@
       <c r="T21" s="9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="22" spans="1:20" ht="27.6">
+      <c r="U21" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="V21" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="W21" s="19" t="s">
+        <v>516</v>
+      </c>
+      <c r="X21" s="19" t="s">
+        <v>565</v>
+      </c>
+      <c r="Y21" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Z21" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="AA21" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="AB21" s="19" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="22" spans="1:28" ht="42.15" customHeight="1">
       <c r="A22" s="7" t="s">
         <v>54</v>
       </c>
@@ -3264,8 +4279,32 @@
       <c r="T22" s="9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="23" spans="1:20" ht="27.6">
+      <c r="U22" s="19" t="s">
+        <v>566</v>
+      </c>
+      <c r="V22" s="19" t="s">
+        <v>567</v>
+      </c>
+      <c r="W22" s="19" t="s">
+        <v>568</v>
+      </c>
+      <c r="X22" s="19" t="s">
+        <v>569</v>
+      </c>
+      <c r="Y22" s="19" t="s">
+        <v>570</v>
+      </c>
+      <c r="Z22" s="19" t="s">
+        <v>571</v>
+      </c>
+      <c r="AA22" s="19" t="s">
+        <v>572</v>
+      </c>
+      <c r="AB22" s="19" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="23" spans="1:28" ht="21.15" customHeight="1">
       <c r="A23" s="7" t="s">
         <v>54</v>
       </c>
@@ -3322,8 +4361,32 @@
       <c r="T23" s="9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="24" spans="1:20" ht="27.6">
+      <c r="U23" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="V23" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="W23" s="19" t="s">
+        <v>505</v>
+      </c>
+      <c r="X23" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Y23" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Z23" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="AA23" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="AB23" s="19" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" spans="1:28" ht="21.15" customHeight="1">
       <c r="A24" s="7" t="s">
         <v>54</v>
       </c>
@@ -3382,8 +4445,32 @@
       <c r="T24" s="9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="25" spans="1:20" ht="27.6">
+      <c r="U24" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="V24" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="W24" s="19" t="s">
+        <v>516</v>
+      </c>
+      <c r="X24" s="19" t="s">
+        <v>574</v>
+      </c>
+      <c r="Y24" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Z24" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="AA24" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="AB24" s="19" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="25" spans="1:28" ht="21.15" customHeight="1">
       <c r="A25" s="7" t="s">
         <v>54</v>
       </c>
@@ -3440,8 +4527,32 @@
       <c r="T25" s="9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="26" spans="1:20" ht="27.6">
+      <c r="U25" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="V25" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="W25" s="19" t="s">
+        <v>516</v>
+      </c>
+      <c r="X25" s="19" t="s">
+        <v>576</v>
+      </c>
+      <c r="Y25" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z25" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA25" s="19" t="s">
+        <v>518</v>
+      </c>
+      <c r="AB25" s="19" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="26" spans="1:28" ht="21.15" customHeight="1">
       <c r="A26" s="7" t="s">
         <v>54</v>
       </c>
@@ -3498,8 +4609,32 @@
       <c r="T26" s="9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="27" spans="1:20" ht="27.6">
+      <c r="U26" s="19" t="s">
+        <v>577</v>
+      </c>
+      <c r="V26" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="W26" s="19" t="s">
+        <v>578</v>
+      </c>
+      <c r="X26" s="19" t="s">
+        <v>579</v>
+      </c>
+      <c r="Y26" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="Z26" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA26" s="19" t="s">
+        <v>540</v>
+      </c>
+      <c r="AB26" s="19" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="27" spans="1:28" ht="21.15" customHeight="1">
       <c r="A27" s="7" t="s">
         <v>54</v>
       </c>
@@ -3556,8 +4691,32 @@
       <c r="T27" s="9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="28" spans="1:20" ht="27.6">
+      <c r="U27" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="V27" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="W27" s="19" t="s">
+        <v>505</v>
+      </c>
+      <c r="X27" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Y27" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Z27" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="AA27" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="AB27" s="19" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="28" spans="1:28" ht="21.15" customHeight="1">
       <c r="A28" s="7" t="s">
         <v>54</v>
       </c>
@@ -3616,8 +4775,32 @@
       <c r="T28" s="9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="29" spans="1:20" ht="27.6">
+      <c r="U28" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="V28" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="W28" s="19" t="s">
+        <v>505</v>
+      </c>
+      <c r="X28" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Y28" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Z28" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="AA28" s="19" t="s">
+        <v>580</v>
+      </c>
+      <c r="AB28" s="19" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="29" spans="1:28" ht="21.15" customHeight="1">
       <c r="A29" s="7" t="s">
         <v>54</v>
       </c>
@@ -3676,8 +4859,32 @@
       <c r="T29" s="9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="30" spans="1:20" ht="27.6">
+      <c r="U29" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="V29" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="W29" s="19" t="s">
+        <v>505</v>
+      </c>
+      <c r="X29" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Y29" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Z29" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="AA29" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="AB29" s="19" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="30" spans="1:28" ht="21.15" customHeight="1">
       <c r="A30" s="7" t="s">
         <v>54</v>
       </c>
@@ -3734,8 +4941,32 @@
       <c r="T30" s="9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="31" spans="1:20" ht="27.6">
+      <c r="U30" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="V30" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="W30" s="19" t="s">
+        <v>505</v>
+      </c>
+      <c r="X30" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Y30" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Z30" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="AA30" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="AB30" s="19" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="31" spans="1:28" ht="31.65" customHeight="1">
       <c r="A31" s="7" t="s">
         <v>54</v>
       </c>
@@ -3794,8 +5025,32 @@
       <c r="T31" s="9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="32" spans="1:20" ht="27.6">
+      <c r="U31" s="19" t="s">
+        <v>583</v>
+      </c>
+      <c r="V31" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="W31" s="19" t="s">
+        <v>584</v>
+      </c>
+      <c r="X31" s="19" t="s">
+        <v>585</v>
+      </c>
+      <c r="Y31" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="Z31" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA31" s="19" t="s">
+        <v>552</v>
+      </c>
+      <c r="AB31" s="19" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="32" spans="1:28" ht="21.15" customHeight="1">
       <c r="A32" s="7" t="s">
         <v>80</v>
       </c>
@@ -3852,8 +5107,32 @@
       <c r="T32" s="9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="33" spans="1:20" ht="27.6">
+      <c r="U32" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="V32" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="W32" s="19" t="s">
+        <v>505</v>
+      </c>
+      <c r="X32" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Y32" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Z32" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="AA32" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="AB32" s="19" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="33" spans="1:28" ht="21.15" customHeight="1">
       <c r="A33" s="7" t="s">
         <v>80</v>
       </c>
@@ -3912,8 +5191,32 @@
       <c r="T33" s="9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="34" spans="1:20" ht="27.6">
+      <c r="U33" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="V33" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="W33" s="19" t="s">
+        <v>516</v>
+      </c>
+      <c r="X33" s="19" t="s">
+        <v>586</v>
+      </c>
+      <c r="Y33" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Z33" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="AA33" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="AB33" s="19" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="34" spans="1:28" ht="21.15" customHeight="1">
       <c r="A34" s="7" t="s">
         <v>80</v>
       </c>
@@ -3972,8 +5275,32 @@
       <c r="T34" s="9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="35" spans="1:20" ht="27.6">
+      <c r="U34" s="19" t="s">
+        <v>588</v>
+      </c>
+      <c r="V34" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="W34" s="19" t="s">
+        <v>516</v>
+      </c>
+      <c r="X34" s="19" t="s">
+        <v>589</v>
+      </c>
+      <c r="Y34" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Z34" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="AA34" s="19" t="s">
+        <v>513</v>
+      </c>
+      <c r="AB34" s="19" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="35" spans="1:28" ht="21.15" customHeight="1">
       <c r="A35" s="7" t="s">
         <v>80</v>
       </c>
@@ -4030,8 +5357,32 @@
       <c r="T35" s="9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="36" spans="1:20" ht="27.6">
+      <c r="U35" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="V35" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="W35" s="19" t="s">
+        <v>590</v>
+      </c>
+      <c r="X35" s="19" t="s">
+        <v>591</v>
+      </c>
+      <c r="Y35" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Z35" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="AA35" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="AB35" s="19" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="36" spans="1:28" ht="21.15" customHeight="1">
       <c r="A36" s="7" t="s">
         <v>80</v>
       </c>
@@ -4088,8 +5439,32 @@
       <c r="T36" s="9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="37" spans="1:20" ht="27.6">
+      <c r="U36" s="19" t="s">
+        <v>592</v>
+      </c>
+      <c r="V36" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="W36" s="19" t="s">
+        <v>516</v>
+      </c>
+      <c r="X36" s="19" t="s">
+        <v>593</v>
+      </c>
+      <c r="Y36" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="Z36" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA36" s="19" t="s">
+        <v>594</v>
+      </c>
+      <c r="AB36" s="19" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="37" spans="1:28" ht="21.15" customHeight="1">
       <c r="A37" s="7" t="s">
         <v>80</v>
       </c>
@@ -4146,8 +5521,32 @@
       <c r="T37" s="9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="38" spans="1:20" ht="27.6">
+      <c r="U37" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="V37" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="W37" s="19" t="s">
+        <v>505</v>
+      </c>
+      <c r="X37" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Y37" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Z37" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="AA37" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="AB37" s="19" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="38" spans="1:28" ht="21.15" customHeight="1">
       <c r="A38" s="7" t="s">
         <v>80</v>
       </c>
@@ -4208,8 +5607,32 @@
       <c r="T38" s="9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="39" spans="1:20" ht="27.6">
+      <c r="U38" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="V38" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="W38" s="19" t="s">
+        <v>505</v>
+      </c>
+      <c r="X38" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Y38" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Z38" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="AA38" s="19" t="s">
+        <v>596</v>
+      </c>
+      <c r="AB38" s="19" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="39" spans="1:28" ht="31.65" customHeight="1">
       <c r="A39" s="7" t="s">
         <v>80</v>
       </c>
@@ -4268,8 +5691,32 @@
       <c r="T39" s="9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="40" spans="1:20" ht="27.6">
+      <c r="U39" s="19" t="s">
+        <v>598</v>
+      </c>
+      <c r="V39" s="19" t="s">
+        <v>599</v>
+      </c>
+      <c r="W39" s="19" t="s">
+        <v>600</v>
+      </c>
+      <c r="X39" s="19" t="s">
+        <v>601</v>
+      </c>
+      <c r="Y39" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="Z39" s="19" t="s">
+        <v>528</v>
+      </c>
+      <c r="AA39" s="19" t="s">
+        <v>529</v>
+      </c>
+      <c r="AB39" s="19" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="40" spans="1:28" ht="21.15" customHeight="1">
       <c r="A40" s="7" t="s">
         <v>80</v>
       </c>
@@ -4328,8 +5775,32 @@
       <c r="T40" s="9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="41" spans="1:20" ht="27.6">
+      <c r="U40" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="V40" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="W40" s="19" t="s">
+        <v>516</v>
+      </c>
+      <c r="X40" s="19" t="s">
+        <v>602</v>
+      </c>
+      <c r="Y40" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Z40" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="AA40" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="AB40" s="19" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="41" spans="1:28" ht="21.15" customHeight="1">
       <c r="A41" s="7" t="s">
         <v>80</v>
       </c>
@@ -4386,8 +5857,32 @@
       <c r="T41" s="9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="42" spans="1:20" ht="27.6">
+      <c r="U41" s="19" t="s">
+        <v>603</v>
+      </c>
+      <c r="V41" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="W41" s="19" t="s">
+        <v>516</v>
+      </c>
+      <c r="X41" s="19" t="s">
+        <v>604</v>
+      </c>
+      <c r="Y41" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Z41" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="AA41" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="AB41" s="19" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="42" spans="1:28" ht="21.15" customHeight="1">
       <c r="A42" s="7" t="s">
         <v>80</v>
       </c>
@@ -4444,8 +5939,32 @@
       <c r="T42" s="9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="43" spans="1:20" ht="27.6">
+      <c r="U42" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="V42" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="W42" s="19" t="s">
+        <v>505</v>
+      </c>
+      <c r="X42" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Y42" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Z42" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="AA42" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="AB42" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="43" spans="1:28" ht="21.15" customHeight="1">
       <c r="A43" s="7" t="s">
         <v>80</v>
       </c>
@@ -4502,8 +6021,32 @@
       <c r="T43" s="9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="44" spans="1:20" ht="27.6">
+      <c r="U43" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="V43" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="W43" s="19" t="s">
+        <v>605</v>
+      </c>
+      <c r="X43" s="19" t="s">
+        <v>606</v>
+      </c>
+      <c r="Y43" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Z43" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="AA43" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="AB43" s="19" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="44" spans="1:28" ht="21.15" customHeight="1">
       <c r="A44" s="7" t="s">
         <v>80</v>
       </c>
@@ -4560,8 +6103,32 @@
       <c r="T44" s="9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="45" spans="1:20" ht="27.6">
+      <c r="U44" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="V44" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="W44" s="19" t="s">
+        <v>505</v>
+      </c>
+      <c r="X44" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Y44" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Z44" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="AA44" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="AB44" s="19" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="45" spans="1:28" ht="21.15" customHeight="1">
       <c r="A45" s="7" t="s">
         <v>80</v>
       </c>
@@ -4618,8 +6185,32 @@
       <c r="T45" s="9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="46" spans="1:20" ht="27.6">
+      <c r="U45" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="V45" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="W45" s="19" t="s">
+        <v>516</v>
+      </c>
+      <c r="X45" s="19" t="s">
+        <v>607</v>
+      </c>
+      <c r="Y45" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Z45" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="AA45" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="AB45" s="19" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="46" spans="1:28" ht="21.15" customHeight="1">
       <c r="A46" s="10" t="s">
         <v>80</v>
       </c>
@@ -4675,6 +6266,30 @@
       </c>
       <c r="T46" s="12" t="s">
         <v>23</v>
+      </c>
+      <c r="U46" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="V46" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="W46" s="19" t="s">
+        <v>516</v>
+      </c>
+      <c r="X46" s="19" t="s">
+        <v>608</v>
+      </c>
+      <c r="Y46" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="Z46" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA46" s="19" t="s">
+        <v>609</v>
+      </c>
+      <c r="AB46" s="19" t="s">
+        <v>610</v>
       </c>
     </row>
   </sheetData>
@@ -4684,7 +6299,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N136"/>
+  <dimension ref="A1:U136"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -4699,9 +6314,16 @@
     <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="20" customWidth="1"/>
     <col min="14" max="14" width="58" customWidth="1"/>
+    <col min="15" max="15" width="36" customWidth="1"/>
+    <col min="16" max="16" width="32" customWidth="1"/>
+    <col min="17" max="17" width="22" customWidth="1"/>
+    <col min="18" max="18" width="42" customWidth="1"/>
+    <col min="19" max="19" width="20" customWidth="1"/>
+    <col min="20" max="20" width="48" customWidth="1"/>
+    <col min="21" max="21" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="19.2" customHeight="1">
+    <row r="1" spans="1:21" ht="21.15" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -4744,8 +6366,29 @@
       <c r="N1" s="3" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" ht="27.6">
+      <c r="O1" s="19" t="s">
+        <v>611</v>
+      </c>
+      <c r="P1" s="19" t="s">
+        <v>497</v>
+      </c>
+      <c r="Q1" s="19" t="s">
+        <v>612</v>
+      </c>
+      <c r="R1" s="19" t="s">
+        <v>499</v>
+      </c>
+      <c r="S1" s="19" t="s">
+        <v>500</v>
+      </c>
+      <c r="T1" s="19" t="s">
+        <v>501</v>
+      </c>
+      <c r="U1" s="19" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" ht="11.1" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>21</v>
       </c>
@@ -4788,8 +6431,29 @@
       <c r="N2" s="6" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" ht="27.6">
+      <c r="O2" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="P2" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q2" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="R2" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="S2" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T2" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U2" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" ht="11.1" customHeight="1">
       <c r="A3" s="7" t="s">
         <v>21</v>
       </c>
@@ -4832,8 +6496,29 @@
       <c r="N3" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" ht="27.6">
+      <c r="O3" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="P3" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q3" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="R3" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="S3" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T3" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U3" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" ht="11.1" customHeight="1">
       <c r="A4" s="7" t="s">
         <v>21</v>
       </c>
@@ -4876,8 +6561,29 @@
       <c r="N4" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" ht="27.6">
+      <c r="O4" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="P4" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q4" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="R4" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="S4" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T4" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U4" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" ht="21.15" customHeight="1">
       <c r="A5" s="7" t="s">
         <v>24</v>
       </c>
@@ -4920,8 +6626,29 @@
       <c r="N5" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" ht="27.6">
+      <c r="O5" s="19" t="s">
+        <v>506</v>
+      </c>
+      <c r="P5" s="19" t="s">
+        <v>506</v>
+      </c>
+      <c r="Q5" s="19" t="s">
+        <v>615</v>
+      </c>
+      <c r="R5" s="19" t="s">
+        <v>508</v>
+      </c>
+      <c r="S5" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T5" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U5" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="21.15" customHeight="1">
       <c r="A6" s="7" t="s">
         <v>24</v>
       </c>
@@ -4964,8 +6691,29 @@
       <c r="N6" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" ht="27.6">
+      <c r="O6" s="19" t="s">
+        <v>506</v>
+      </c>
+      <c r="P6" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q6" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R6" s="19" t="s">
+        <v>508</v>
+      </c>
+      <c r="S6" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T6" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U6" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="21.15" customHeight="1">
       <c r="A7" s="7" t="s">
         <v>24</v>
       </c>
@@ -5008,8 +6756,29 @@
       <c r="N7" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" ht="27.6">
+      <c r="O7" s="19" t="s">
+        <v>506</v>
+      </c>
+      <c r="P7" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q7" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R7" s="19" t="s">
+        <v>508</v>
+      </c>
+      <c r="S7" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T7" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U7" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" ht="21.15" customHeight="1">
       <c r="A8" s="7" t="s">
         <v>27</v>
       </c>
@@ -5052,8 +6821,29 @@
       <c r="N8" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" ht="27.6">
+      <c r="O8" s="19" t="s">
+        <v>617</v>
+      </c>
+      <c r="P8" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q8" s="19" t="s">
+        <v>615</v>
+      </c>
+      <c r="R8" s="19" t="s">
+        <v>512</v>
+      </c>
+      <c r="S8" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="T8" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="U8" s="19" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" ht="21.15" customHeight="1">
       <c r="A9" s="7" t="s">
         <v>27</v>
       </c>
@@ -5096,8 +6886,29 @@
       <c r="N9" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" ht="27.6">
+      <c r="O9" s="19" t="s">
+        <v>617</v>
+      </c>
+      <c r="P9" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q9" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R9" s="19" t="s">
+        <v>512</v>
+      </c>
+      <c r="S9" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="T9" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="U9" s="19" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" ht="21.15" customHeight="1">
       <c r="A10" s="7" t="s">
         <v>27</v>
       </c>
@@ -5140,8 +6951,29 @@
       <c r="N10" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" ht="27.6">
+      <c r="O10" s="19" t="s">
+        <v>617</v>
+      </c>
+      <c r="P10" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q10" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R10" s="19" t="s">
+        <v>512</v>
+      </c>
+      <c r="S10" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="T10" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="U10" s="19" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" ht="21.15" customHeight="1">
       <c r="A11" s="7" t="s">
         <v>29</v>
       </c>
@@ -5184,8 +7016,29 @@
       <c r="N11" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" ht="27.6">
+      <c r="O11" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="P11" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q11" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R11" s="19" t="s">
+        <v>517</v>
+      </c>
+      <c r="S11" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T11" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U11" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" ht="21.15" customHeight="1">
       <c r="A12" s="7" t="s">
         <v>29</v>
       </c>
@@ -5228,8 +7081,29 @@
       <c r="N12" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" ht="27.6">
+      <c r="O12" s="19" t="s">
+        <v>515</v>
+      </c>
+      <c r="P12" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q12" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R12" s="19" t="s">
+        <v>517</v>
+      </c>
+      <c r="S12" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T12" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U12" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" ht="21.15" customHeight="1">
       <c r="A13" s="7" t="s">
         <v>29</v>
       </c>
@@ -5272,8 +7146,29 @@
       <c r="N13" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" ht="27.6">
+      <c r="O13" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="P13" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q13" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R13" s="19" t="s">
+        <v>517</v>
+      </c>
+      <c r="S13" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T13" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U13" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" ht="21.15" customHeight="1">
       <c r="A14" s="7" t="s">
         <v>32</v>
       </c>
@@ -5316,8 +7211,29 @@
       <c r="N14" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" ht="27.6">
+      <c r="O14" s="19" t="s">
+        <v>520</v>
+      </c>
+      <c r="P14" s="19" t="s">
+        <v>521</v>
+      </c>
+      <c r="Q14" s="19" t="s">
+        <v>615</v>
+      </c>
+      <c r="R14" s="19" t="s">
+        <v>523</v>
+      </c>
+      <c r="S14" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T14" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U14" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" ht="21.15" customHeight="1">
       <c r="A15" s="7" t="s">
         <v>32</v>
       </c>
@@ -5360,8 +7276,29 @@
       <c r="N15" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" ht="27.6">
+      <c r="O15" s="19" t="s">
+        <v>520</v>
+      </c>
+      <c r="P15" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q15" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R15" s="19" t="s">
+        <v>523</v>
+      </c>
+      <c r="S15" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T15" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U15" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" ht="21.15" customHeight="1">
       <c r="A16" s="7" t="s">
         <v>32</v>
       </c>
@@ -5404,8 +7341,29 @@
       <c r="N16" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="17" spans="1:14" ht="27.6">
+      <c r="O16" s="19" t="s">
+        <v>520</v>
+      </c>
+      <c r="P16" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q16" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R16" s="19" t="s">
+        <v>523</v>
+      </c>
+      <c r="S16" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T16" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U16" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" ht="21.15" customHeight="1">
       <c r="A17" s="7" t="s">
         <v>34</v>
       </c>
@@ -5448,8 +7406,29 @@
       <c r="N17" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="18" spans="1:14" ht="27.6">
+      <c r="O17" s="19" t="s">
+        <v>525</v>
+      </c>
+      <c r="P17" s="19" t="s">
+        <v>525</v>
+      </c>
+      <c r="Q17" s="19" t="s">
+        <v>615</v>
+      </c>
+      <c r="R17" s="19" t="s">
+        <v>527</v>
+      </c>
+      <c r="S17" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="T17" s="19" t="s">
+        <v>528</v>
+      </c>
+      <c r="U17" s="19" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" ht="21.15" customHeight="1">
       <c r="A18" s="7" t="s">
         <v>34</v>
       </c>
@@ -5492,8 +7471,29 @@
       <c r="N18" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="19" spans="1:14" ht="27.6">
+      <c r="O18" s="19" t="s">
+        <v>525</v>
+      </c>
+      <c r="P18" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q18" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R18" s="19" t="s">
+        <v>527</v>
+      </c>
+      <c r="S18" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="T18" s="19" t="s">
+        <v>528</v>
+      </c>
+      <c r="U18" s="19" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" ht="21.15" customHeight="1">
       <c r="A19" s="7" t="s">
         <v>34</v>
       </c>
@@ -5536,8 +7536,29 @@
       <c r="N19" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="20" spans="1:14" ht="27.6">
+      <c r="O19" s="19" t="s">
+        <v>525</v>
+      </c>
+      <c r="P19" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q19" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R19" s="19" t="s">
+        <v>527</v>
+      </c>
+      <c r="S19" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="T19" s="19" t="s">
+        <v>528</v>
+      </c>
+      <c r="U19" s="19" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" ht="21.15" customHeight="1">
       <c r="A20" s="7" t="s">
         <v>35</v>
       </c>
@@ -5580,8 +7601,29 @@
       <c r="N20" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="21" spans="1:14" ht="27.6">
+      <c r="O20" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="P20" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q20" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R20" s="19" t="s">
+        <v>531</v>
+      </c>
+      <c r="S20" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T20" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U20" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" ht="21.15" customHeight="1">
       <c r="A21" s="7" t="s">
         <v>35</v>
       </c>
@@ -5624,8 +7666,29 @@
       <c r="N21" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="22" spans="1:14" ht="27.6">
+      <c r="O21" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="P21" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q21" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R21" s="19" t="s">
+        <v>531</v>
+      </c>
+      <c r="S21" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T21" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U21" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" ht="21.15" customHeight="1">
       <c r="A22" s="7" t="s">
         <v>35</v>
       </c>
@@ -5668,8 +7731,29 @@
       <c r="N22" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="23" spans="1:14" ht="27.6">
+      <c r="O22" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="P22" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q22" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R22" s="19" t="s">
+        <v>531</v>
+      </c>
+      <c r="S22" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T22" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U22" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" ht="21.15" customHeight="1">
       <c r="A23" s="7" t="s">
         <v>38</v>
       </c>
@@ -5712,8 +7796,29 @@
       <c r="N23" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="24" spans="1:14" ht="27.6">
+      <c r="O23" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="P23" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q23" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R23" s="19" t="s">
+        <v>534</v>
+      </c>
+      <c r="S23" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T23" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U23" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" ht="21.15" customHeight="1">
       <c r="A24" s="7" t="s">
         <v>38</v>
       </c>
@@ -5756,8 +7861,29 @@
       <c r="N24" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="25" spans="1:14" ht="27.6">
+      <c r="O24" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="P24" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q24" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R24" s="19" t="s">
+        <v>534</v>
+      </c>
+      <c r="S24" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T24" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U24" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" ht="21.15" customHeight="1">
       <c r="A25" s="7" t="s">
         <v>38</v>
       </c>
@@ -5800,8 +7926,29 @@
       <c r="N25" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="26" spans="1:14" ht="27.6">
+      <c r="O25" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="P25" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q25" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R25" s="19" t="s">
+        <v>534</v>
+      </c>
+      <c r="S25" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T25" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U25" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" ht="21.15" customHeight="1">
       <c r="A26" s="7" t="s">
         <v>41</v>
       </c>
@@ -5844,8 +7991,29 @@
       <c r="N26" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="27" spans="1:14" ht="27.6">
+      <c r="O26" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="P26" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q26" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="R26" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="S26" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T26" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U26" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" ht="21.15" customHeight="1">
       <c r="A27" s="7" t="s">
         <v>41</v>
       </c>
@@ -5888,8 +8056,29 @@
       <c r="N27" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="28" spans="1:14" ht="27.6">
+      <c r="O27" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="P27" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q27" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="R27" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="S27" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T27" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U27" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" ht="21.15" customHeight="1">
       <c r="A28" s="7" t="s">
         <v>41</v>
       </c>
@@ -5932,8 +8121,29 @@
       <c r="N28" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="29" spans="1:14" ht="27.6">
+      <c r="O28" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="P28" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q28" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="R28" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="S28" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T28" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U28" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" ht="21.15" customHeight="1">
       <c r="A29" s="7" t="s">
         <v>43</v>
       </c>
@@ -5976,8 +8186,29 @@
       <c r="N29" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="30" spans="1:14" ht="27.6">
+      <c r="O29" s="19" t="s">
+        <v>619</v>
+      </c>
+      <c r="P29" s="19" t="s">
+        <v>537</v>
+      </c>
+      <c r="Q29" s="19" t="s">
+        <v>615</v>
+      </c>
+      <c r="R29" s="19" t="s">
+        <v>539</v>
+      </c>
+      <c r="S29" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="T29" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="U29" s="19" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" ht="21.15" customHeight="1">
       <c r="A30" s="7" t="s">
         <v>43</v>
       </c>
@@ -6020,8 +8251,29 @@
       <c r="N30" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="31" spans="1:14" ht="27.6">
+      <c r="O30" s="19" t="s">
+        <v>619</v>
+      </c>
+      <c r="P30" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q30" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R30" s="19" t="s">
+        <v>539</v>
+      </c>
+      <c r="S30" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="T30" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="U30" s="19" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" ht="21.15" customHeight="1">
       <c r="A31" s="7" t="s">
         <v>43</v>
       </c>
@@ -6064,8 +8316,29 @@
       <c r="N31" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="32" spans="1:14" ht="27.6">
+      <c r="O31" s="19" t="s">
+        <v>619</v>
+      </c>
+      <c r="P31" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q31" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R31" s="19" t="s">
+        <v>539</v>
+      </c>
+      <c r="S31" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="T31" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="U31" s="19" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" ht="21.15" customHeight="1">
       <c r="A32" s="7" t="s">
         <v>44</v>
       </c>
@@ -6108,8 +8381,29 @@
       <c r="N32" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="33" spans="1:14" ht="27.6">
+      <c r="O32" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="P32" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q32" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="R32" s="19" t="s">
+        <v>542</v>
+      </c>
+      <c r="S32" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T32" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U32" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" ht="21.15" customHeight="1">
       <c r="A33" s="7" t="s">
         <v>44</v>
       </c>
@@ -6152,8 +8446,29 @@
       <c r="N33" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="34" spans="1:14" ht="27.6">
+      <c r="O33" s="19" t="s">
+        <v>544</v>
+      </c>
+      <c r="P33" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q33" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R33" s="19" t="s">
+        <v>542</v>
+      </c>
+      <c r="S33" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T33" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U33" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" ht="21.15" customHeight="1">
       <c r="A34" s="7" t="s">
         <v>44</v>
       </c>
@@ -6196,8 +8511,29 @@
       <c r="N34" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="35" spans="1:14" ht="27.6">
+      <c r="O34" s="19" t="s">
+        <v>544</v>
+      </c>
+      <c r="P34" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q34" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R34" s="19" t="s">
+        <v>542</v>
+      </c>
+      <c r="S34" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T34" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U34" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" ht="21.15" customHeight="1">
       <c r="A35" s="7" t="s">
         <v>47</v>
       </c>
@@ -6240,8 +8576,29 @@
       <c r="N35" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="36" spans="1:14" ht="27.6">
+      <c r="O35" s="19" t="s">
+        <v>544</v>
+      </c>
+      <c r="P35" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q35" s="19" t="s">
+        <v>615</v>
+      </c>
+      <c r="R35" s="19" t="s">
+        <v>546</v>
+      </c>
+      <c r="S35" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="T35" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="U35" s="19" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" ht="21.15" customHeight="1">
       <c r="A36" s="7" t="s">
         <v>47</v>
       </c>
@@ -6284,8 +8641,29 @@
       <c r="N36" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="37" spans="1:14" ht="27.6">
+      <c r="O36" s="19" t="s">
+        <v>544</v>
+      </c>
+      <c r="P36" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q36" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R36" s="19" t="s">
+        <v>546</v>
+      </c>
+      <c r="S36" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="T36" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="U36" s="19" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" ht="21.15" customHeight="1">
       <c r="A37" s="7" t="s">
         <v>47</v>
       </c>
@@ -6328,8 +8706,29 @@
       <c r="N37" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="38" spans="1:14" ht="27.6">
+      <c r="O37" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="P37" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q37" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="R37" s="19" t="s">
+        <v>546</v>
+      </c>
+      <c r="S37" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="T37" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="U37" s="19" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" ht="21.15" customHeight="1">
       <c r="A38" s="7" t="s">
         <v>48</v>
       </c>
@@ -6372,8 +8771,29 @@
       <c r="N38" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="39" spans="1:14" ht="27.6">
+      <c r="O38" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="P38" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q38" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="R38" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="S38" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T38" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U38" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" ht="21.15" customHeight="1">
       <c r="A39" s="7" t="s">
         <v>48</v>
       </c>
@@ -6416,8 +8836,29 @@
       <c r="N39" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="40" spans="1:14" ht="27.6">
+      <c r="O39" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="P39" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q39" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="R39" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="S39" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T39" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U39" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21" ht="21.15" customHeight="1">
       <c r="A40" s="7" t="s">
         <v>48</v>
       </c>
@@ -6460,8 +8901,29 @@
       <c r="N40" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="41" spans="1:14" ht="27.6">
+      <c r="O40" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="P40" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q40" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="R40" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="S40" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T40" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U40" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21" ht="11.1" customHeight="1">
       <c r="A41" s="7" t="s">
         <v>50</v>
       </c>
@@ -6504,8 +8966,29 @@
       <c r="N41" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="42" spans="1:14" ht="27.6">
+      <c r="O41" s="19" t="s">
+        <v>620</v>
+      </c>
+      <c r="P41" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q41" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R41" s="19" t="s">
+        <v>547</v>
+      </c>
+      <c r="S41" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T41" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U41" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21" ht="11.1" customHeight="1">
       <c r="A42" s="7" t="s">
         <v>50</v>
       </c>
@@ -6548,8 +9031,29 @@
       <c r="N42" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="43" spans="1:14" ht="27.6">
+      <c r="O42" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="P42" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q42" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R42" s="19" t="s">
+        <v>547</v>
+      </c>
+      <c r="S42" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T42" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U42" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21" ht="11.1" customHeight="1">
       <c r="A43" s="7" t="s">
         <v>50</v>
       </c>
@@ -6592,8 +9096,29 @@
       <c r="N43" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="44" spans="1:14" ht="27.6">
+      <c r="O43" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="P43" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q43" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R43" s="19" t="s">
+        <v>547</v>
+      </c>
+      <c r="S43" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T43" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U43" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21" ht="31.65" customHeight="1">
       <c r="A44" s="7" t="s">
         <v>52</v>
       </c>
@@ -6636,8 +9161,29 @@
       <c r="N44" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="45" spans="1:14" ht="27.6">
+      <c r="O44" s="19" t="s">
+        <v>621</v>
+      </c>
+      <c r="P44" s="19" t="s">
+        <v>549</v>
+      </c>
+      <c r="Q44" s="19" t="s">
+        <v>615</v>
+      </c>
+      <c r="R44" s="19" t="s">
+        <v>551</v>
+      </c>
+      <c r="S44" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="T44" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="U44" s="19" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21" ht="31.65" customHeight="1">
       <c r="A45" s="7" t="s">
         <v>52</v>
       </c>
@@ -6680,8 +9226,29 @@
       <c r="N45" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="46" spans="1:14" ht="27.6">
+      <c r="O45" s="19" t="s">
+        <v>621</v>
+      </c>
+      <c r="P45" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q45" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R45" s="19" t="s">
+        <v>551</v>
+      </c>
+      <c r="S45" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="T45" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="U45" s="19" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21" ht="31.65" customHeight="1">
       <c r="A46" s="7" t="s">
         <v>52</v>
       </c>
@@ -6724,8 +9291,29 @@
       <c r="N46" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="47" spans="1:14" ht="27.6">
+      <c r="O46" s="19" t="s">
+        <v>622</v>
+      </c>
+      <c r="P46" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q46" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R46" s="19" t="s">
+        <v>551</v>
+      </c>
+      <c r="S46" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="T46" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="U46" s="19" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21" ht="21.15" customHeight="1">
       <c r="A47" s="7" t="s">
         <v>55</v>
       </c>
@@ -6768,8 +9356,29 @@
       <c r="N47" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="48" spans="1:14" ht="27.6">
+      <c r="O47" s="19" t="s">
+        <v>554</v>
+      </c>
+      <c r="P47" s="19" t="s">
+        <v>554</v>
+      </c>
+      <c r="Q47" s="19" t="s">
+        <v>615</v>
+      </c>
+      <c r="R47" s="19" t="s">
+        <v>556</v>
+      </c>
+      <c r="S47" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T47" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U47" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21" ht="21.15" customHeight="1">
       <c r="A48" s="7" t="s">
         <v>55</v>
       </c>
@@ -6812,8 +9421,29 @@
       <c r="N48" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="49" spans="1:14" ht="27.6">
+      <c r="O48" s="19" t="s">
+        <v>554</v>
+      </c>
+      <c r="P48" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q48" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R48" s="19" t="s">
+        <v>556</v>
+      </c>
+      <c r="S48" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T48" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U48" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21" ht="21.15" customHeight="1">
       <c r="A49" s="7" t="s">
         <v>55</v>
       </c>
@@ -6856,8 +9486,29 @@
       <c r="N49" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="50" spans="1:14" ht="27.6">
+      <c r="O49" s="19" t="s">
+        <v>554</v>
+      </c>
+      <c r="P49" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q49" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R49" s="19" t="s">
+        <v>556</v>
+      </c>
+      <c r="S49" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T49" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U49" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21" ht="21.15" customHeight="1">
       <c r="A50" s="7" t="s">
         <v>56</v>
       </c>
@@ -6900,8 +9551,29 @@
       <c r="N50" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="51" spans="1:14" ht="27.6">
+      <c r="O50" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="P50" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q50" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R50" s="19" t="s">
+        <v>557</v>
+      </c>
+      <c r="S50" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T50" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U50" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="51" spans="1:21" ht="21.15" customHeight="1">
       <c r="A51" s="7" t="s">
         <v>56</v>
       </c>
@@ -6944,8 +9616,29 @@
       <c r="N51" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="52" spans="1:14" ht="27.6">
+      <c r="O51" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="P51" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q51" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R51" s="19" t="s">
+        <v>557</v>
+      </c>
+      <c r="S51" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T51" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U51" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="52" spans="1:21" ht="21.15" customHeight="1">
       <c r="A52" s="7" t="s">
         <v>56</v>
       </c>
@@ -6988,8 +9681,29 @@
       <c r="N52" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="53" spans="1:14" ht="27.6">
+      <c r="O52" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="P52" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q52" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R52" s="19" t="s">
+        <v>557</v>
+      </c>
+      <c r="S52" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T52" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U52" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="53" spans="1:21" ht="21.15" customHeight="1">
       <c r="A53" s="7" t="s">
         <v>59</v>
       </c>
@@ -7032,8 +9746,29 @@
       <c r="N53" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="54" spans="1:14" ht="27.6">
+      <c r="O53" s="19" t="s">
+        <v>623</v>
+      </c>
+      <c r="P53" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q53" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R53" s="19" t="s">
+        <v>561</v>
+      </c>
+      <c r="S53" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T53" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U53" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="54" spans="1:21" ht="21.15" customHeight="1">
       <c r="A54" s="7" t="s">
         <v>59</v>
       </c>
@@ -7076,8 +9811,29 @@
       <c r="N54" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="55" spans="1:14" ht="27.6">
+      <c r="O54" s="19" t="s">
+        <v>624</v>
+      </c>
+      <c r="P54" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q54" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R54" s="19" t="s">
+        <v>561</v>
+      </c>
+      <c r="S54" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T54" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U54" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="55" spans="1:21" ht="21.15" customHeight="1">
       <c r="A55" s="7" t="s">
         <v>59</v>
       </c>
@@ -7120,8 +9876,29 @@
       <c r="N55" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="56" spans="1:14" ht="27.6">
+      <c r="O55" s="19" t="s">
+        <v>560</v>
+      </c>
+      <c r="P55" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q55" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R55" s="19" t="s">
+        <v>561</v>
+      </c>
+      <c r="S55" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T55" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U55" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21" ht="21.15" customHeight="1">
       <c r="A56" s="7" t="s">
         <v>60</v>
       </c>
@@ -7164,8 +9941,29 @@
       <c r="N56" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="57" spans="1:14" ht="27.6">
+      <c r="O56" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="P56" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q56" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R56" s="19" t="s">
+        <v>564</v>
+      </c>
+      <c r="S56" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T56" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U56" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21" ht="21.15" customHeight="1">
       <c r="A57" s="7" t="s">
         <v>60</v>
       </c>
@@ -7208,8 +10006,29 @@
       <c r="N57" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="58" spans="1:14" ht="27.6">
+      <c r="O57" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="P57" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q57" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R57" s="19" t="s">
+        <v>564</v>
+      </c>
+      <c r="S57" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T57" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U57" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21" ht="21.15" customHeight="1">
       <c r="A58" s="7" t="s">
         <v>60</v>
       </c>
@@ -7252,8 +10071,29 @@
       <c r="N58" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="59" spans="1:14" ht="27.6">
+      <c r="O58" s="19" t="s">
+        <v>563</v>
+      </c>
+      <c r="P58" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q58" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R58" s="19" t="s">
+        <v>564</v>
+      </c>
+      <c r="S58" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T58" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U58" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21" ht="21.15" customHeight="1">
       <c r="A59" s="7" t="s">
         <v>61</v>
       </c>
@@ -7296,8 +10136,29 @@
       <c r="N59" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="60" spans="1:14" ht="27.6">
+      <c r="O59" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="P59" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q59" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R59" s="19" t="s">
+        <v>565</v>
+      </c>
+      <c r="S59" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T59" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U59" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="60" spans="1:21" ht="21.15" customHeight="1">
       <c r="A60" s="7" t="s">
         <v>61</v>
       </c>
@@ -7340,8 +10201,29 @@
       <c r="N60" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="61" spans="1:14" ht="27.6">
+      <c r="O60" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="P60" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q60" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R60" s="19" t="s">
+        <v>565</v>
+      </c>
+      <c r="S60" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T60" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U60" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="61" spans="1:21" ht="21.15" customHeight="1">
       <c r="A61" s="7" t="s">
         <v>61</v>
       </c>
@@ -7384,8 +10266,29 @@
       <c r="N61" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="62" spans="1:14" ht="27.6">
+      <c r="O61" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="P61" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q61" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R61" s="19" t="s">
+        <v>565</v>
+      </c>
+      <c r="S61" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T61" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U61" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="62" spans="1:21" ht="31.65" customHeight="1">
       <c r="A62" s="7" t="s">
         <v>63</v>
       </c>
@@ -7428,8 +10331,29 @@
       <c r="N62" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="63" spans="1:14" ht="27.6">
+      <c r="O62" s="19" t="s">
+        <v>567</v>
+      </c>
+      <c r="P62" s="19" t="s">
+        <v>567</v>
+      </c>
+      <c r="Q62" s="19" t="s">
+        <v>615</v>
+      </c>
+      <c r="R62" s="19" t="s">
+        <v>569</v>
+      </c>
+      <c r="S62" s="19" t="s">
+        <v>570</v>
+      </c>
+      <c r="T62" s="19" t="s">
+        <v>571</v>
+      </c>
+      <c r="U62" s="19" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="63" spans="1:21" ht="31.65" customHeight="1">
       <c r="A63" s="7" t="s">
         <v>63</v>
       </c>
@@ -7472,8 +10396,29 @@
       <c r="N63" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="64" spans="1:14" ht="27.6">
+      <c r="O63" s="19" t="s">
+        <v>567</v>
+      </c>
+      <c r="P63" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q63" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R63" s="19" t="s">
+        <v>569</v>
+      </c>
+      <c r="S63" s="19" t="s">
+        <v>570</v>
+      </c>
+      <c r="T63" s="19" t="s">
+        <v>571</v>
+      </c>
+      <c r="U63" s="19" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="64" spans="1:21" ht="31.65" customHeight="1">
       <c r="A64" s="7" t="s">
         <v>63</v>
       </c>
@@ -7516,8 +10461,29 @@
       <c r="N64" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="65" spans="1:14" ht="27.6">
+      <c r="O64" s="19" t="s">
+        <v>567</v>
+      </c>
+      <c r="P64" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q64" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R64" s="19" t="s">
+        <v>569</v>
+      </c>
+      <c r="S64" s="19" t="s">
+        <v>570</v>
+      </c>
+      <c r="T64" s="19" t="s">
+        <v>571</v>
+      </c>
+      <c r="U64" s="19" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21" ht="11.1" customHeight="1">
       <c r="A65" s="7" t="s">
         <v>64</v>
       </c>
@@ -7560,8 +10526,29 @@
       <c r="N65" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="66" spans="1:14" ht="27.6">
+      <c r="O65" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="P65" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q65" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="R65" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="S65" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T65" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U65" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="66" spans="1:21" ht="11.1" customHeight="1">
       <c r="A66" s="7" t="s">
         <v>64</v>
       </c>
@@ -7604,8 +10591,29 @@
       <c r="N66" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="67" spans="1:14" ht="27.6">
+      <c r="O66" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="P66" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q66" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="R66" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="S66" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T66" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U66" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="67" spans="1:21" ht="11.1" customHeight="1">
       <c r="A67" s="7" t="s">
         <v>64</v>
       </c>
@@ -7648,8 +10656,29 @@
       <c r="N67" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="68" spans="1:14" ht="27.6">
+      <c r="O67" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="P67" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q67" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="R67" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="S67" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T67" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U67" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="68" spans="1:21" ht="21.15" customHeight="1">
       <c r="A68" s="7" t="s">
         <v>66</v>
       </c>
@@ -7692,8 +10721,29 @@
       <c r="N68" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="69" spans="1:14" ht="27.6">
+      <c r="O68" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="P68" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q68" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R68" s="19" t="s">
+        <v>574</v>
+      </c>
+      <c r="S68" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T68" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U68" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="69" spans="1:21" ht="21.15" customHeight="1">
       <c r="A69" s="7" t="s">
         <v>66</v>
       </c>
@@ -7736,8 +10786,29 @@
       <c r="N69" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="70" spans="1:14" ht="27.6">
+      <c r="O69" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="P69" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q69" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R69" s="19" t="s">
+        <v>574</v>
+      </c>
+      <c r="S69" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T69" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U69" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="70" spans="1:21" ht="21.15" customHeight="1">
       <c r="A70" s="7" t="s">
         <v>66</v>
       </c>
@@ -7780,8 +10851,29 @@
       <c r="N70" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="71" spans="1:14" ht="27.6">
+      <c r="O70" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="P70" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q70" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R70" s="19" t="s">
+        <v>574</v>
+      </c>
+      <c r="S70" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T70" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U70" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="71" spans="1:21" ht="21.15" customHeight="1">
       <c r="A71" s="7" t="s">
         <v>67</v>
       </c>
@@ -7824,8 +10916,29 @@
       <c r="N71" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="72" spans="1:14" ht="27.6">
+      <c r="O71" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="P71" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q71" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="R71" s="19" t="s">
+        <v>576</v>
+      </c>
+      <c r="S71" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="T71" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="U71" s="19" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="72" spans="1:21" ht="21.15" customHeight="1">
       <c r="A72" s="7" t="s">
         <v>67</v>
       </c>
@@ -7868,8 +10981,29 @@
       <c r="N72" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="73" spans="1:14" ht="27.6">
+      <c r="O72" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="P72" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q72" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R72" s="19" t="s">
+        <v>576</v>
+      </c>
+      <c r="S72" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="T72" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="U72" s="19" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="73" spans="1:21" ht="21.15" customHeight="1">
       <c r="A73" s="7" t="s">
         <v>67</v>
       </c>
@@ -7912,8 +11046,29 @@
       <c r="N73" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="74" spans="1:14" ht="27.6">
+      <c r="O73" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="P73" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q73" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="R73" s="19" t="s">
+        <v>576</v>
+      </c>
+      <c r="S73" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="T73" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="U73" s="19" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="74" spans="1:21" ht="21.15" customHeight="1">
       <c r="A74" s="7" t="s">
         <v>68</v>
       </c>
@@ -7956,8 +11111,29 @@
       <c r="N74" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="75" spans="1:14" ht="27.6">
+      <c r="O74" s="19" t="s">
+        <v>625</v>
+      </c>
+      <c r="P74" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q74" s="19" t="s">
+        <v>615</v>
+      </c>
+      <c r="R74" s="19" t="s">
+        <v>579</v>
+      </c>
+      <c r="S74" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="T74" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="U74" s="19" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="75" spans="1:21" ht="21.15" customHeight="1">
       <c r="A75" s="7" t="s">
         <v>68</v>
       </c>
@@ -8000,8 +11176,29 @@
       <c r="N75" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="76" spans="1:14" ht="27.6">
+      <c r="O75" s="19" t="s">
+        <v>625</v>
+      </c>
+      <c r="P75" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q75" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R75" s="19" t="s">
+        <v>579</v>
+      </c>
+      <c r="S75" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="T75" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="U75" s="19" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="76" spans="1:21" ht="21.15" customHeight="1">
       <c r="A76" s="7" t="s">
         <v>68</v>
       </c>
@@ -8044,8 +11241,29 @@
       <c r="N76" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="77" spans="1:14" ht="27.6">
+      <c r="O76" s="19" t="s">
+        <v>626</v>
+      </c>
+      <c r="P76" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q76" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R76" s="19" t="s">
+        <v>579</v>
+      </c>
+      <c r="S76" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="T76" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="U76" s="19" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="77" spans="1:21" ht="21.15" customHeight="1">
       <c r="A77" s="7" t="s">
         <v>69</v>
       </c>
@@ -8088,8 +11306,29 @@
       <c r="N77" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="78" spans="1:14" ht="27.6">
+      <c r="O77" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="P77" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q77" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="R77" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="S77" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T77" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U77" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="78" spans="1:21" ht="21.15" customHeight="1">
       <c r="A78" s="7" t="s">
         <v>69</v>
       </c>
@@ -8132,8 +11371,29 @@
       <c r="N78" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="79" spans="1:14" ht="27.6">
+      <c r="O78" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="P78" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q78" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="R78" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="S78" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T78" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U78" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="79" spans="1:21" ht="21.15" customHeight="1">
       <c r="A79" s="7" t="s">
         <v>69</v>
       </c>
@@ -8176,8 +11436,29 @@
       <c r="N79" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="80" spans="1:14" ht="27.6">
+      <c r="O79" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="P79" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q79" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="R79" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="S79" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T79" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U79" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="80" spans="1:21" ht="21.15" customHeight="1">
       <c r="A80" s="7" t="s">
         <v>71</v>
       </c>
@@ -8220,8 +11501,29 @@
       <c r="N80" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="81" spans="1:14" ht="27.6">
+      <c r="O80" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="P80" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q80" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R80" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="S80" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T80" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U80" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="81" spans="1:21" ht="21.15" customHeight="1">
       <c r="A81" s="7" t="s">
         <v>71</v>
       </c>
@@ -8264,8 +11566,29 @@
       <c r="N81" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="82" spans="1:14" ht="27.6">
+      <c r="O81" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="P81" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q81" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R81" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="S81" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T81" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U81" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="82" spans="1:21" ht="21.15" customHeight="1">
       <c r="A82" s="7" t="s">
         <v>71</v>
       </c>
@@ -8308,8 +11631,29 @@
       <c r="N82" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="83" spans="1:14" ht="27.6">
+      <c r="O82" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="P82" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q82" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R82" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="S82" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T82" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U82" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="83" spans="1:21" ht="21.15" customHeight="1">
       <c r="A83" s="7" t="s">
         <v>74</v>
       </c>
@@ -8352,8 +11696,29 @@
       <c r="N83" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="84" spans="1:14" ht="27.6">
+      <c r="O83" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="P83" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q83" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="R83" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="S83" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T83" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U83" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="84" spans="1:21" ht="21.15" customHeight="1">
       <c r="A84" s="7" t="s">
         <v>74</v>
       </c>
@@ -8396,8 +11761,29 @@
       <c r="N84" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="85" spans="1:14" ht="27.6">
+      <c r="O84" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="P84" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q84" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="R84" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="S84" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T84" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U84" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="85" spans="1:21" ht="21.15" customHeight="1">
       <c r="A85" s="7" t="s">
         <v>74</v>
       </c>
@@ -8440,8 +11826,29 @@
       <c r="N85" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="86" spans="1:14" ht="27.6">
+      <c r="O85" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="P85" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q85" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="R85" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="S85" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T85" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U85" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="86" spans="1:21" ht="21.15" customHeight="1">
       <c r="A86" s="7" t="s">
         <v>77</v>
       </c>
@@ -8484,8 +11891,29 @@
       <c r="N86" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="87" spans="1:14" ht="27.6">
+      <c r="O86" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="P86" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q86" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="R86" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="S86" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T86" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U86" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="87" spans="1:21" ht="21.15" customHeight="1">
       <c r="A87" s="7" t="s">
         <v>77</v>
       </c>
@@ -8528,8 +11956,29 @@
       <c r="N87" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="88" spans="1:14" ht="27.6">
+      <c r="O87" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="P87" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q87" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="R87" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="S87" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T87" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U87" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="88" spans="1:21" ht="21.15" customHeight="1">
       <c r="A88" s="7" t="s">
         <v>77</v>
       </c>
@@ -8572,8 +12021,29 @@
       <c r="N88" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="89" spans="1:14" ht="27.6">
+      <c r="O88" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="P88" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q88" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="R88" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="S88" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T88" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U88" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="89" spans="1:21" ht="31.65" customHeight="1">
       <c r="A89" s="7" t="s">
         <v>79</v>
       </c>
@@ -8616,8 +12086,29 @@
       <c r="N89" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="90" spans="1:14" ht="27.6">
+      <c r="O89" s="19" t="s">
+        <v>627</v>
+      </c>
+      <c r="P89" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q89" s="19" t="s">
+        <v>615</v>
+      </c>
+      <c r="R89" s="19" t="s">
+        <v>585</v>
+      </c>
+      <c r="S89" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="T89" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="U89" s="19" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="90" spans="1:21" ht="31.65" customHeight="1">
       <c r="A90" s="7" t="s">
         <v>79</v>
       </c>
@@ -8660,8 +12151,29 @@
       <c r="N90" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="91" spans="1:14" ht="27.6">
+      <c r="O90" s="19" t="s">
+        <v>627</v>
+      </c>
+      <c r="P90" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q90" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R90" s="19" t="s">
+        <v>585</v>
+      </c>
+      <c r="S90" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="T90" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="U90" s="19" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="91" spans="1:21" ht="31.65" customHeight="1">
       <c r="A91" s="7" t="s">
         <v>79</v>
       </c>
@@ -8704,8 +12216,29 @@
       <c r="N91" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="92" spans="1:14" ht="27.6">
+      <c r="O91" s="19" t="s">
+        <v>628</v>
+      </c>
+      <c r="P91" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q91" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R91" s="19" t="s">
+        <v>585</v>
+      </c>
+      <c r="S91" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="T91" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="U91" s="19" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="92" spans="1:21" ht="11.1" customHeight="1">
       <c r="A92" s="7" t="s">
         <v>81</v>
       </c>
@@ -8748,8 +12281,29 @@
       <c r="N92" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="93" spans="1:14" ht="27.6">
+      <c r="O92" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="P92" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q92" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R92" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="S92" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T92" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U92" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="93" spans="1:21" ht="11.1" customHeight="1">
       <c r="A93" s="7" t="s">
         <v>81</v>
       </c>
@@ -8792,8 +12346,29 @@
       <c r="N93" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="94" spans="1:14" ht="27.6">
+      <c r="O93" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="P93" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q93" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="R93" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="S93" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T93" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U93" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="94" spans="1:21" ht="11.1" customHeight="1">
       <c r="A94" s="7" t="s">
         <v>81</v>
       </c>
@@ -8836,8 +12411,29 @@
       <c r="N94" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="95" spans="1:14" ht="27.6">
+      <c r="O94" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="P94" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q94" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="R94" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="S94" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T94" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U94" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="95" spans="1:21" ht="21.15" customHeight="1">
       <c r="A95" s="7" t="s">
         <v>83</v>
       </c>
@@ -8880,8 +12476,29 @@
       <c r="N95" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="96" spans="1:14" ht="27.6">
+      <c r="O95" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="P95" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q95" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R95" s="19" t="s">
+        <v>586</v>
+      </c>
+      <c r="S95" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T95" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U95" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="96" spans="1:21" ht="21.15" customHeight="1">
       <c r="A96" s="7" t="s">
         <v>83</v>
       </c>
@@ -8924,8 +12541,29 @@
       <c r="N96" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="97" spans="1:14" ht="27.6">
+      <c r="O96" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="P96" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q96" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R96" s="19" t="s">
+        <v>586</v>
+      </c>
+      <c r="S96" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T96" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U96" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="97" spans="1:21" ht="21.15" customHeight="1">
       <c r="A97" s="7" t="s">
         <v>83</v>
       </c>
@@ -8968,8 +12606,29 @@
       <c r="N97" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="98" spans="1:14" ht="27.6">
+      <c r="O97" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="P97" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q97" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R97" s="19" t="s">
+        <v>586</v>
+      </c>
+      <c r="S97" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T97" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U97" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="98" spans="1:21" ht="21.15" customHeight="1">
       <c r="A98" s="7" t="s">
         <v>84</v>
       </c>
@@ -9012,8 +12671,29 @@
       <c r="N98" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="99" spans="1:14" ht="27.6">
+      <c r="O98" s="19" t="s">
+        <v>629</v>
+      </c>
+      <c r="P98" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q98" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R98" s="19" t="s">
+        <v>589</v>
+      </c>
+      <c r="S98" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T98" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U98" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="99" spans="1:21" ht="21.15" customHeight="1">
       <c r="A99" s="7" t="s">
         <v>84</v>
       </c>
@@ -9056,8 +12736,29 @@
       <c r="N99" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="100" spans="1:14" ht="27.6">
+      <c r="O99" s="19" t="s">
+        <v>629</v>
+      </c>
+      <c r="P99" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q99" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R99" s="19" t="s">
+        <v>589</v>
+      </c>
+      <c r="S99" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T99" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U99" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="100" spans="1:21" ht="21.15" customHeight="1">
       <c r="A100" s="7" t="s">
         <v>84</v>
       </c>
@@ -9100,8 +12801,29 @@
       <c r="N100" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="101" spans="1:14" ht="27.6">
+      <c r="O100" s="19" t="s">
+        <v>629</v>
+      </c>
+      <c r="P100" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q100" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R100" s="19" t="s">
+        <v>589</v>
+      </c>
+      <c r="S100" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T100" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U100" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="101" spans="1:21" ht="21.15" customHeight="1">
       <c r="A101" s="7" t="s">
         <v>85</v>
       </c>
@@ -9144,8 +12866,29 @@
       <c r="N101" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="102" spans="1:14" ht="27.6">
+      <c r="O101" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="P101" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q101" s="19" t="s">
+        <v>615</v>
+      </c>
+      <c r="R101" s="19" t="s">
+        <v>591</v>
+      </c>
+      <c r="S101" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T101" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U101" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="102" spans="1:21" ht="21.15" customHeight="1">
       <c r="A102" s="7" t="s">
         <v>85</v>
       </c>
@@ -9188,8 +12931,29 @@
       <c r="N102" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="103" spans="1:14" ht="27.6">
+      <c r="O102" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="P102" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q102" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R102" s="19" t="s">
+        <v>591</v>
+      </c>
+      <c r="S102" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T102" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U102" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="103" spans="1:21" ht="21.15" customHeight="1">
       <c r="A103" s="7" t="s">
         <v>85</v>
       </c>
@@ -9232,8 +12996,29 @@
       <c r="N103" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="104" spans="1:14" ht="27.6">
+      <c r="O103" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="P103" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q103" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R103" s="19" t="s">
+        <v>591</v>
+      </c>
+      <c r="S103" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T103" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U103" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="104" spans="1:21" ht="11.1" customHeight="1">
       <c r="A104" s="7" t="s">
         <v>87</v>
       </c>
@@ -9276,8 +13061,29 @@
       <c r="N104" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="105" spans="1:14" ht="27.6">
+      <c r="O104" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="P104" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q104" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R104" s="19" t="s">
+        <v>593</v>
+      </c>
+      <c r="S104" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="T104" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="U104" s="19" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="105" spans="1:21" ht="11.1" customHeight="1">
       <c r="A105" s="7" t="s">
         <v>87</v>
       </c>
@@ -9320,8 +13126,29 @@
       <c r="N105" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="106" spans="1:14" ht="27.6">
+      <c r="O105" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="P105" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q105" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R105" s="19" t="s">
+        <v>593</v>
+      </c>
+      <c r="S105" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="T105" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="U105" s="19" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="106" spans="1:21" ht="11.1" customHeight="1">
       <c r="A106" s="7" t="s">
         <v>87</v>
       </c>
@@ -9364,8 +13191,29 @@
       <c r="N106" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="107" spans="1:14" ht="27.6">
+      <c r="O106" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="P106" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q106" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R106" s="19" t="s">
+        <v>593</v>
+      </c>
+      <c r="S106" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="T106" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="U106" s="19" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="107" spans="1:21" ht="11.1" customHeight="1">
       <c r="A107" s="7" t="s">
         <v>88</v>
       </c>
@@ -9408,8 +13256,29 @@
       <c r="N107" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="108" spans="1:14" ht="27.6">
+      <c r="O107" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="P107" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q107" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="R107" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="S107" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T107" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U107" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="108" spans="1:21" ht="11.1" customHeight="1">
       <c r="A108" s="7" t="s">
         <v>88</v>
       </c>
@@ -9452,8 +13321,29 @@
       <c r="N108" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="109" spans="1:14" ht="27.6">
+      <c r="O108" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="P108" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q108" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="R108" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="S108" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T108" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U108" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="109" spans="1:21" ht="11.1" customHeight="1">
       <c r="A109" s="7" t="s">
         <v>88</v>
       </c>
@@ -9496,8 +13386,29 @@
       <c r="N109" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="110" spans="1:14" ht="27.6">
+      <c r="O109" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="P109" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q109" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="R109" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="S109" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T109" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U109" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="110" spans="1:21" ht="21.15" customHeight="1">
       <c r="A110" s="7" t="s">
         <v>90</v>
       </c>
@@ -9540,8 +13451,29 @@
       <c r="N110" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="111" spans="1:14" ht="27.6">
+      <c r="O110" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="P110" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q110" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="R110" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="S110" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T110" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U110" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="111" spans="1:21" ht="21.15" customHeight="1">
       <c r="A111" s="7" t="s">
         <v>90</v>
       </c>
@@ -9584,8 +13516,29 @@
       <c r="N111" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="112" spans="1:14" ht="27.6">
+      <c r="O111" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="P111" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q111" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="R111" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="S111" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T111" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U111" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="112" spans="1:21" ht="21.15" customHeight="1">
       <c r="A112" s="7" t="s">
         <v>90</v>
       </c>
@@ -9628,8 +13581,29 @@
       <c r="N112" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="113" spans="1:14" ht="27.6">
+      <c r="O112" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="P112" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q112" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="R112" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="S112" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T112" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U112" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="113" spans="1:21" ht="21.15" customHeight="1">
       <c r="A113" s="7" t="s">
         <v>94</v>
       </c>
@@ -9672,8 +13646,29 @@
       <c r="N113" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="114" spans="1:14" ht="27.6">
+      <c r="O113" s="19" t="s">
+        <v>599</v>
+      </c>
+      <c r="P113" s="19" t="s">
+        <v>599</v>
+      </c>
+      <c r="Q113" s="19" t="s">
+        <v>615</v>
+      </c>
+      <c r="R113" s="19" t="s">
+        <v>601</v>
+      </c>
+      <c r="S113" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="T113" s="19" t="s">
+        <v>528</v>
+      </c>
+      <c r="U113" s="19" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="114" spans="1:21" ht="21.15" customHeight="1">
       <c r="A114" s="7" t="s">
         <v>94</v>
       </c>
@@ -9716,8 +13711,29 @@
       <c r="N114" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="115" spans="1:14" ht="27.6">
+      <c r="O114" s="19" t="s">
+        <v>599</v>
+      </c>
+      <c r="P114" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q114" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R114" s="19" t="s">
+        <v>601</v>
+      </c>
+      <c r="S114" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="T114" s="19" t="s">
+        <v>528</v>
+      </c>
+      <c r="U114" s="19" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="115" spans="1:21" ht="21.15" customHeight="1">
       <c r="A115" s="7" t="s">
         <v>94</v>
       </c>
@@ -9760,8 +13776,29 @@
       <c r="N115" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="116" spans="1:14" ht="27.6">
+      <c r="O115" s="19" t="s">
+        <v>599</v>
+      </c>
+      <c r="P115" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q115" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R115" s="19" t="s">
+        <v>601</v>
+      </c>
+      <c r="S115" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="T115" s="19" t="s">
+        <v>528</v>
+      </c>
+      <c r="U115" s="19" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="116" spans="1:21" ht="21.15" customHeight="1">
       <c r="A116" s="7" t="s">
         <v>95</v>
       </c>
@@ -9804,8 +13841,29 @@
       <c r="N116" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="117" spans="1:14" ht="27.6">
+      <c r="O116" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="P116" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q116" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R116" s="19" t="s">
+        <v>602</v>
+      </c>
+      <c r="S116" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T116" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U116" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="117" spans="1:21" ht="21.15" customHeight="1">
       <c r="A117" s="7" t="s">
         <v>95</v>
       </c>
@@ -9848,8 +13906,29 @@
       <c r="N117" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="118" spans="1:14" ht="27.6">
+      <c r="O117" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="P117" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q117" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R117" s="19" t="s">
+        <v>602</v>
+      </c>
+      <c r="S117" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T117" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U117" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="118" spans="1:21" ht="21.15" customHeight="1">
       <c r="A118" s="7" t="s">
         <v>95</v>
       </c>
@@ -9892,8 +13971,29 @@
       <c r="N118" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="119" spans="1:14" ht="27.6">
+      <c r="O118" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="P118" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q118" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R118" s="19" t="s">
+        <v>602</v>
+      </c>
+      <c r="S118" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T118" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U118" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="119" spans="1:21" ht="21.15" customHeight="1">
       <c r="A119" s="7" t="s">
         <v>96</v>
       </c>
@@ -9936,8 +14036,29 @@
       <c r="N119" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="120" spans="1:14" ht="27.6">
+      <c r="O119" s="19" t="s">
+        <v>603</v>
+      </c>
+      <c r="P119" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q119" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R119" s="19" t="s">
+        <v>604</v>
+      </c>
+      <c r="S119" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T119" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U119" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="120" spans="1:21" ht="21.15" customHeight="1">
       <c r="A120" s="7" t="s">
         <v>96</v>
       </c>
@@ -9980,8 +14101,29 @@
       <c r="N120" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="121" spans="1:14" ht="27.6">
+      <c r="O120" s="19" t="s">
+        <v>603</v>
+      </c>
+      <c r="P120" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q120" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R120" s="19" t="s">
+        <v>604</v>
+      </c>
+      <c r="S120" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T120" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U120" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="121" spans="1:21" ht="21.15" customHeight="1">
       <c r="A121" s="7" t="s">
         <v>96</v>
       </c>
@@ -10024,8 +14166,29 @@
       <c r="N121" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="122" spans="1:14" ht="27.6">
+      <c r="O121" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="P121" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q121" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R121" s="19" t="s">
+        <v>604</v>
+      </c>
+      <c r="S121" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T121" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U121" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="122" spans="1:21" ht="21.15" customHeight="1">
       <c r="A122" s="7" t="s">
         <v>97</v>
       </c>
@@ -10068,8 +14231,29 @@
       <c r="N122" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="123" spans="1:14" ht="27.6">
+      <c r="O122" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="P122" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q122" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="R122" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="S122" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T122" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U122" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="123" spans="1:21" ht="21.15" customHeight="1">
       <c r="A123" s="7" t="s">
         <v>97</v>
       </c>
@@ -10112,8 +14296,29 @@
       <c r="N123" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="124" spans="1:14" ht="27.6">
+      <c r="O123" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="P123" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q123" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="R123" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="S123" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T123" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U123" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="124" spans="1:21" ht="21.15" customHeight="1">
       <c r="A124" s="7" t="s">
         <v>97</v>
       </c>
@@ -10156,8 +14361,29 @@
       <c r="N124" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="125" spans="1:14" ht="27.6">
+      <c r="O124" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="P124" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q124" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="R124" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="S124" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T124" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U124" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="125" spans="1:21" ht="21.15" customHeight="1">
       <c r="A125" s="7" t="s">
         <v>99</v>
       </c>
@@ -10200,8 +14426,29 @@
       <c r="N125" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="126" spans="1:14" ht="27.6">
+      <c r="O125" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="P125" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q125" s="19" t="s">
+        <v>615</v>
+      </c>
+      <c r="R125" s="19" t="s">
+        <v>606</v>
+      </c>
+      <c r="S125" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T125" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U125" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="126" spans="1:21" ht="21.15" customHeight="1">
       <c r="A126" s="7" t="s">
         <v>99</v>
       </c>
@@ -10244,8 +14491,29 @@
       <c r="N126" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="127" spans="1:14" ht="27.6">
+      <c r="O126" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="P126" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q126" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R126" s="19" t="s">
+        <v>606</v>
+      </c>
+      <c r="S126" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T126" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U126" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="127" spans="1:21" ht="21.15" customHeight="1">
       <c r="A127" s="7" t="s">
         <v>99</v>
       </c>
@@ -10288,8 +14556,29 @@
       <c r="N127" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="128" spans="1:14" ht="27.6">
+      <c r="O127" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="P127" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q127" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R127" s="19" t="s">
+        <v>606</v>
+      </c>
+      <c r="S127" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T127" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U127" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="128" spans="1:21" ht="21.15" customHeight="1">
       <c r="A128" s="7" t="s">
         <v>100</v>
       </c>
@@ -10332,8 +14621,29 @@
       <c r="N128" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="129" spans="1:14" ht="27.6">
+      <c r="O128" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="P128" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q128" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="R128" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="S128" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T128" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U128" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="129" spans="1:21" ht="21.15" customHeight="1">
       <c r="A129" s="7" t="s">
         <v>100</v>
       </c>
@@ -10376,8 +14686,29 @@
       <c r="N129" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="130" spans="1:14" ht="27.6">
+      <c r="O129" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="P129" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q129" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="R129" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="S129" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T129" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U129" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="130" spans="1:21" ht="21.15" customHeight="1">
       <c r="A130" s="7" t="s">
         <v>100</v>
       </c>
@@ -10420,8 +14751,29 @@
       <c r="N130" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="131" spans="1:14" ht="27.6">
+      <c r="O130" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="P130" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q130" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="R130" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="S130" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T130" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U130" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="131" spans="1:21" ht="21.15" customHeight="1">
       <c r="A131" s="7" t="s">
         <v>102</v>
       </c>
@@ -10464,8 +14816,29 @@
       <c r="N131" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="132" spans="1:14" ht="27.6">
+      <c r="O131" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="P131" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q131" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="R131" s="19" t="s">
+        <v>607</v>
+      </c>
+      <c r="S131" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T131" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U131" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="132" spans="1:21" ht="21.15" customHeight="1">
       <c r="A132" s="7" t="s">
         <v>102</v>
       </c>
@@ -10508,8 +14881,29 @@
       <c r="N132" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="133" spans="1:14" ht="27.6">
+      <c r="O132" s="19" t="s">
+        <v>630</v>
+      </c>
+      <c r="P132" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q132" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R132" s="19" t="s">
+        <v>607</v>
+      </c>
+      <c r="S132" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T132" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U132" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="133" spans="1:21" ht="21.15" customHeight="1">
       <c r="A133" s="7" t="s">
         <v>102</v>
       </c>
@@ -10552,8 +14946,29 @@
       <c r="N133" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="134" spans="1:14" ht="27.6">
+      <c r="O133" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="P133" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q133" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R133" s="19" t="s">
+        <v>607</v>
+      </c>
+      <c r="S133" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="T133" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="U133" s="19" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="134" spans="1:21" ht="21.15" customHeight="1">
       <c r="A134" s="7" t="s">
         <v>103</v>
       </c>
@@ -10596,8 +15011,29 @@
       <c r="N134" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="135" spans="1:14" ht="27.6">
+      <c r="O134" s="19" t="s">
+        <v>603</v>
+      </c>
+      <c r="P134" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q134" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R134" s="19" t="s">
+        <v>608</v>
+      </c>
+      <c r="S134" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="T134" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="U134" s="19" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="135" spans="1:21" ht="21.15" customHeight="1">
       <c r="A135" s="7" t="s">
         <v>103</v>
       </c>
@@ -10640,8 +15076,29 @@
       <c r="N135" s="9" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="136" spans="1:14" ht="27.6">
+      <c r="O135" s="19" t="s">
+        <v>520</v>
+      </c>
+      <c r="P135" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q135" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R135" s="19" t="s">
+        <v>608</v>
+      </c>
+      <c r="S135" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="T135" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="U135" s="19" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="136" spans="1:21" ht="21.15" customHeight="1">
       <c r="A136" s="10" t="s">
         <v>103</v>
       </c>
@@ -10683,6 +15140,27 @@
       </c>
       <c r="N136" s="12" t="s">
         <v>117</v>
+      </c>
+      <c r="O136" s="19" t="s">
+        <v>603</v>
+      </c>
+      <c r="P136" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q136" s="19" t="s">
+        <v>616</v>
+      </c>
+      <c r="R136" s="19" t="s">
+        <v>608</v>
+      </c>
+      <c r="S136" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="T136" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="U136" s="19" t="s">
+        <v>618</v>
       </c>
     </row>
   </sheetData>
@@ -10692,7 +15170,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:N35"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -10701,9 +15179,16 @@
     <col min="5" max="5" width="30" customWidth="1"/>
     <col min="6" max="6" width="28" customWidth="1"/>
     <col min="7" max="7" width="48" customWidth="1"/>
+    <col min="8" max="8" width="36" customWidth="1"/>
+    <col min="9" max="9" width="32" customWidth="1"/>
+    <col min="10" max="10" width="42" customWidth="1"/>
+    <col min="11" max="11" width="20" customWidth="1"/>
+    <col min="12" max="12" width="48" customWidth="1"/>
+    <col min="13" max="13" width="24" customWidth="1"/>
+    <col min="14" max="14" width="62" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="19.2" customHeight="1">
+    <row r="1" spans="1:14" ht="11.1" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>154</v>
       </c>
@@ -10725,8 +15210,29 @@
       <c r="G1" s="3" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="27.6">
+      <c r="H1" s="19" t="s">
+        <v>611</v>
+      </c>
+      <c r="I1" s="19" t="s">
+        <v>497</v>
+      </c>
+      <c r="J1" s="19" t="s">
+        <v>499</v>
+      </c>
+      <c r="K1" s="19" t="s">
+        <v>500</v>
+      </c>
+      <c r="L1" s="19" t="s">
+        <v>501</v>
+      </c>
+      <c r="M1" s="19" t="s">
+        <v>502</v>
+      </c>
+      <c r="N1" s="19" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="21.15" customHeight="1">
       <c r="A2" s="16">
         <v>41715</v>
       </c>
@@ -10748,8 +15254,29 @@
       <c r="G2" s="6" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="27.6">
+      <c r="H2" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="I2" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="J2" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="K2" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="L2" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="M2" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="N2" s="19" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="21.15" customHeight="1">
       <c r="A3" s="17">
         <v>41872</v>
       </c>
@@ -10771,8 +15298,29 @@
       <c r="G3" s="9" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="27.6">
+      <c r="H3" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="I3" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="J3" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="K3" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="L3" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="M3" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="N3" s="19" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="21.15" customHeight="1">
       <c r="A4" s="17">
         <v>42033</v>
       </c>
@@ -10794,8 +15342,29 @@
       <c r="G4" s="9" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" ht="27.6">
+      <c r="H4" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="I4" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="J4" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="K4" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="L4" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="M4" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="N4" s="19" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="21.15" customHeight="1">
       <c r="A5" s="17">
         <v>42207</v>
       </c>
@@ -10817,8 +15386,29 @@
       <c r="G5" s="9" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" ht="27.6">
+      <c r="H5" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="I5" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="J5" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="K5" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="L5" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="M5" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="N5" s="19" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="21.15" customHeight="1">
       <c r="A6" s="17">
         <v>42331</v>
       </c>
@@ -10840,8 +15430,29 @@
       <c r="G6" s="9" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" ht="27.6">
+      <c r="H6" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="I6" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="J6" s="19" t="s">
+        <v>631</v>
+      </c>
+      <c r="K6" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="L6" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="M6" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="N6" s="19" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="42.15" customHeight="1">
       <c r="A7" s="17">
         <v>42338</v>
       </c>
@@ -10863,8 +15474,29 @@
       <c r="G7" s="9" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" ht="27.6">
+      <c r="H7" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="I7" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="J7" s="19" t="s">
+        <v>632</v>
+      </c>
+      <c r="K7" s="19" t="s">
+        <v>570</v>
+      </c>
+      <c r="L7" s="19" t="s">
+        <v>571</v>
+      </c>
+      <c r="M7" s="19" t="s">
+        <v>572</v>
+      </c>
+      <c r="N7" s="19" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="21.15" customHeight="1">
       <c r="A8" s="17">
         <v>42345</v>
       </c>
@@ -10886,8 +15518,29 @@
       <c r="G8" s="9" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" ht="27.6">
+      <c r="H8" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="I8" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="J8" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="K8" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="L8" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="M8" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="N8" s="19" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="21.15" customHeight="1">
       <c r="A9" s="17">
         <v>42381</v>
       </c>
@@ -10909,8 +15562,29 @@
       <c r="G9" s="9" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" ht="27.6">
+      <c r="H9" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="I9" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="J9" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="K9" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="L9" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="M9" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="N9" s="19" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="21.15" customHeight="1">
       <c r="A10" s="17">
         <v>42717</v>
       </c>
@@ -10932,8 +15606,29 @@
       <c r="G10" s="9" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" ht="27.6">
+      <c r="H10" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="I10" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="J10" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="K10" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="L10" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="M10" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="N10" s="19" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="21.15" customHeight="1">
       <c r="A11" s="17">
         <v>42748</v>
       </c>
@@ -10955,8 +15650,29 @@
       <c r="G11" s="9" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" ht="27.6">
+      <c r="H11" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="I11" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="J11" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="K11" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="L11" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="M11" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="N11" s="19" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="21.15" customHeight="1">
       <c r="A12" s="17">
         <v>42893</v>
       </c>
@@ -10978,8 +15694,29 @@
       <c r="G12" s="9" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" ht="27.6">
+      <c r="H12" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="I12" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="J12" s="19" t="s">
+        <v>634</v>
+      </c>
+      <c r="K12" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="L12" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="M12" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="N12" s="19" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="21.15" customHeight="1">
       <c r="A13" s="17">
         <v>42941</v>
       </c>
@@ -11001,8 +15738,29 @@
       <c r="G13" s="9" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" ht="27.6">
+      <c r="H13" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="I13" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="J13" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="K13" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="L13" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="M13" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="N13" s="19" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="21.15" customHeight="1">
       <c r="A14" s="17">
         <v>43532</v>
       </c>
@@ -11024,8 +15782,29 @@
       <c r="G14" s="9" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" ht="27.6">
+      <c r="H14" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="I14" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="J14" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="K14" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="L14" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="M14" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="N14" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="21.15" customHeight="1">
       <c r="A15" s="17">
         <v>43740</v>
       </c>
@@ -11047,8 +15826,29 @@
       <c r="G15" s="9" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" ht="27.6">
+      <c r="H15" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="I15" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="J15" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="K15" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="L15" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="M15" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="N15" s="19" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="21.15" customHeight="1">
       <c r="A16" s="17">
         <v>43836</v>
       </c>
@@ -11070,8 +15870,29 @@
       <c r="G16" s="9" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" ht="27.6">
+      <c r="H16" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="I16" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="J16" s="19" t="s">
+        <v>636</v>
+      </c>
+      <c r="K16" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="L16" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="M16" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="N16" s="19" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="21.15" customHeight="1">
       <c r="A17" s="17">
         <v>43839</v>
       </c>
@@ -11093,8 +15914,29 @@
       <c r="G17" s="9" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" ht="27.6">
+      <c r="H17" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="I17" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="J17" s="19" t="s">
+        <v>637</v>
+      </c>
+      <c r="K17" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="L17" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="M17" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="N17" s="19" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="21.15" customHeight="1">
       <c r="A18" s="17">
         <v>44322</v>
       </c>
@@ -11116,8 +15958,29 @@
       <c r="G18" s="9" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" ht="27.6">
+      <c r="H18" s="19" t="s">
+        <v>544</v>
+      </c>
+      <c r="I18" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="J18" s="19" t="s">
+        <v>542</v>
+      </c>
+      <c r="K18" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="L18" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="M18" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="N18" s="19" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="21.15" customHeight="1">
       <c r="A19" s="17">
         <v>44336</v>
       </c>
@@ -11139,8 +16002,29 @@
       <c r="G19" s="9" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" ht="27.6">
+      <c r="H19" s="19" t="s">
+        <v>638</v>
+      </c>
+      <c r="I19" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="J19" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="K19" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="L19" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="M19" s="19" t="s">
+        <v>203</v>
+      </c>
+      <c r="N19" s="19" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="21.15" customHeight="1">
       <c r="A20" s="17">
         <v>44337</v>
       </c>
@@ -11162,8 +16046,29 @@
       <c r="G20" s="9" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" ht="27.6">
+      <c r="H20" s="19" t="s">
+        <v>629</v>
+      </c>
+      <c r="I20" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="J20" s="19" t="s">
+        <v>640</v>
+      </c>
+      <c r="K20" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="L20" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="M20" s="19" t="s">
+        <v>203</v>
+      </c>
+      <c r="N20" s="19" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="21.15" customHeight="1">
       <c r="A21" s="17">
         <v>44348</v>
       </c>
@@ -11185,8 +16090,29 @@
       <c r="G21" s="9" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" ht="27.6">
+      <c r="H21" s="19" t="s">
+        <v>544</v>
+      </c>
+      <c r="I21" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="J21" s="19" t="s">
+        <v>641</v>
+      </c>
+      <c r="K21" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="L21" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="M21" s="19" t="s">
+        <v>513</v>
+      </c>
+      <c r="N21" s="19" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="21.15" customHeight="1">
       <c r="A22" s="17">
         <v>44621</v>
       </c>
@@ -11208,8 +16134,29 @@
       <c r="G22" s="9" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" ht="27.6">
+      <c r="H22" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="I22" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="J22" s="19" t="s">
+        <v>643</v>
+      </c>
+      <c r="K22" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="L22" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="M22" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="N22" s="19" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="21.15" customHeight="1">
       <c r="A23" s="17">
         <v>44628</v>
       </c>
@@ -11231,8 +16178,29 @@
       <c r="G23" s="9" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" ht="27.6">
+      <c r="H23" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="I23" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="J23" s="19" t="s">
+        <v>644</v>
+      </c>
+      <c r="K23" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="L23" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="M23" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="N23" s="19" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="21.15" customHeight="1">
       <c r="A24" s="17">
         <v>44757</v>
       </c>
@@ -11254,8 +16222,29 @@
       <c r="G24" s="9" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" ht="27.6">
+      <c r="H24" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="I24" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="J24" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="K24" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="L24" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="M24" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="N24" s="19" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="21.15" customHeight="1">
       <c r="A25" s="17">
         <v>45070</v>
       </c>
@@ -11277,8 +16266,29 @@
       <c r="G25" s="9" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" ht="27.6">
+      <c r="H25" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="I25" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="J25" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="K25" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="L25" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="M25" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="N25" s="19" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="21.15" customHeight="1">
       <c r="A26" s="17">
         <v>45226</v>
       </c>
@@ -11300,8 +16310,29 @@
       <c r="G26" s="9" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" ht="27.6">
+      <c r="H26" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="I26" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="J26" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="K26" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="L26" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="M26" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="N26" s="19" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="21.15" customHeight="1">
       <c r="A27" s="17">
         <v>45722</v>
       </c>
@@ -11323,8 +16354,29 @@
       <c r="G27" s="9" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" ht="27.6">
+      <c r="H27" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="I27" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="J27" s="19" t="s">
+        <v>645</v>
+      </c>
+      <c r="K27" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="L27" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="M27" s="19" t="s">
+        <v>518</v>
+      </c>
+      <c r="N27" s="19" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="21.15" customHeight="1">
       <c r="A28" s="17">
         <v>45729</v>
       </c>
@@ -11346,8 +16398,29 @@
       <c r="G28" s="9" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" ht="27.6">
+      <c r="H28" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="I28" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="J28" s="19" t="s">
+        <v>647</v>
+      </c>
+      <c r="K28" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="L28" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="M28" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="N28" s="19" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="21.15" customHeight="1">
       <c r="A29" s="17">
         <v>45813</v>
       </c>
@@ -11369,8 +16442,29 @@
       <c r="G29" s="9" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" ht="27.6">
+      <c r="H29" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="I29" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="J29" s="19" t="s">
+        <v>648</v>
+      </c>
+      <c r="K29" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="L29" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="M29" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="N29" s="19" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="21.15" customHeight="1">
       <c r="A30" s="17">
         <v>45828</v>
       </c>
@@ -11392,8 +16486,29 @@
       <c r="G30" s="9" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" ht="27.6">
+      <c r="H30" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="I30" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="J30" s="19" t="s">
+        <v>649</v>
+      </c>
+      <c r="K30" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="L30" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="M30" s="19" t="s">
+        <v>594</v>
+      </c>
+      <c r="N30" s="19" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="21.15" customHeight="1">
       <c r="A31" s="17">
         <v>45832</v>
       </c>
@@ -11415,8 +16530,29 @@
       <c r="G31" s="9" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" ht="27.6">
+      <c r="H31" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="I31" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="J31" s="19" t="s">
+        <v>651</v>
+      </c>
+      <c r="K31" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="L31" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="M31" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="N31" s="19" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="21.15" customHeight="1">
       <c r="A32" s="17">
         <v>46091</v>
       </c>
@@ -11438,8 +16574,29 @@
       <c r="G32" s="9" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" ht="27.6">
+      <c r="H32" s="19" t="s">
+        <v>520</v>
+      </c>
+      <c r="I32" s="19" t="s">
+        <v>521</v>
+      </c>
+      <c r="J32" s="19" t="s">
+        <v>652</v>
+      </c>
+      <c r="K32" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="L32" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="M32" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="N32" s="19" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" ht="21.15" customHeight="1">
       <c r="A33" s="17">
         <v>46098</v>
       </c>
@@ -11461,8 +16618,29 @@
       <c r="G33" s="9" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" ht="41.4">
+      <c r="H33" s="19" t="s">
+        <v>653</v>
+      </c>
+      <c r="I33" s="19" t="s">
+        <v>653</v>
+      </c>
+      <c r="J33" s="19" t="s">
+        <v>654</v>
+      </c>
+      <c r="K33" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="L33" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="M33" s="19" t="s">
+        <v>540</v>
+      </c>
+      <c r="N33" s="19" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" ht="31.65" customHeight="1">
       <c r="A34" s="17">
         <v>46105</v>
       </c>
@@ -11484,8 +16662,29 @@
       <c r="G34" s="9" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" ht="27.6">
+      <c r="H34" s="19" t="s">
+        <v>656</v>
+      </c>
+      <c r="I34" s="19" t="s">
+        <v>657</v>
+      </c>
+      <c r="J34" s="19" t="s">
+        <v>658</v>
+      </c>
+      <c r="K34" s="19" t="s">
+        <v>609</v>
+      </c>
+      <c r="L34" s="19" t="s">
+        <v>610</v>
+      </c>
+      <c r="M34" s="19" t="s">
+        <v>223</v>
+      </c>
+      <c r="N34" s="19" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" ht="21.15" customHeight="1">
       <c r="A35" s="18">
         <v>46112</v>
       </c>
@@ -11506,6 +16705,27 @@
       </c>
       <c r="G35" s="12" t="s">
         <v>163</v>
+      </c>
+      <c r="H35" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="I35" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="J35" s="19" t="s">
+        <v>604</v>
+      </c>
+      <c r="K35" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="L35" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="M35" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="N35" s="19" t="s">
+        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -11527,7 +16747,7 @@
     <col min="7" max="7" width="95" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="19.2" customHeight="1">
+    <row r="1" spans="1:7" ht="15.3" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>225</v>
       </c>
@@ -11550,7 +16770,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="26.85" customHeight="1">
+    <row r="2" spans="1:7" ht="21.45" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>232</v>
       </c>
@@ -11573,7 +16793,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="26.85" customHeight="1">
+    <row r="3" spans="1:7" ht="21.45" customHeight="1">
       <c r="A3" s="7" t="s">
         <v>239</v>
       </c>
@@ -11596,7 +16816,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="26.85" customHeight="1">
+    <row r="4" spans="1:7" ht="21.45" customHeight="1">
       <c r="A4" s="7" t="s">
         <v>246</v>
       </c>
@@ -11619,7 +16839,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="26.85" customHeight="1">
+    <row r="5" spans="1:7" ht="21.45" customHeight="1">
       <c r="A5" s="7" t="s">
         <v>252</v>
       </c>
@@ -11642,7 +16862,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="26.85" customHeight="1">
+    <row r="6" spans="1:7" ht="21.45" customHeight="1">
       <c r="A6" s="7" t="s">
         <v>258</v>
       </c>
@@ -11665,7 +16885,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="26.85" customHeight="1">
+    <row r="7" spans="1:7" ht="21.45" customHeight="1">
       <c r="A7" s="7" t="s">
         <v>265</v>
       </c>
@@ -11688,7 +16908,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="26.85" customHeight="1">
+    <row r="8" spans="1:7" ht="21.45" customHeight="1">
       <c r="A8" s="7" t="s">
         <v>272</v>
       </c>
@@ -11711,7 +16931,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="26.85" customHeight="1">
+    <row r="9" spans="1:7" ht="21.45" customHeight="1">
       <c r="A9" s="7" t="s">
         <v>279</v>
       </c>
@@ -11734,7 +16954,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="26.85" customHeight="1">
+    <row r="10" spans="1:7" ht="21.45" customHeight="1">
       <c r="A10" s="7" t="s">
         <v>286</v>
       </c>
@@ -11757,7 +16977,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="26.85" customHeight="1">
+    <row r="11" spans="1:7" ht="21.45" customHeight="1">
       <c r="A11" s="7" t="s">
         <v>293</v>
       </c>
@@ -11780,7 +17000,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="26.85" customHeight="1">
+    <row r="12" spans="1:7" ht="21.45" customHeight="1">
       <c r="A12" s="7" t="s">
         <v>300</v>
       </c>
@@ -11803,7 +17023,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="26.85" customHeight="1">
+    <row r="13" spans="1:7" ht="21.45" customHeight="1">
       <c r="A13" s="7" t="s">
         <v>307</v>
       </c>
@@ -11826,7 +17046,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="26.85" customHeight="1">
+    <row r="14" spans="1:7" ht="21.45" customHeight="1">
       <c r="A14" s="7" t="s">
         <v>314</v>
       </c>
@@ -11849,7 +17069,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="26.85" customHeight="1">
+    <row r="15" spans="1:7" ht="21.45" customHeight="1">
       <c r="A15" s="7" t="s">
         <v>321</v>
       </c>
@@ -11872,7 +17092,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="26.85" customHeight="1">
+    <row r="16" spans="1:7" ht="21.45" customHeight="1">
       <c r="A16" s="7" t="s">
         <v>328</v>
       </c>
@@ -11895,7 +17115,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="26.85" customHeight="1">
+    <row r="17" spans="1:7" ht="21.45" customHeight="1">
       <c r="A17" s="7" t="s">
         <v>335</v>
       </c>
@@ -11918,7 +17138,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="26.85" customHeight="1">
+    <row r="18" spans="1:7" ht="21.45" customHeight="1">
       <c r="A18" s="7" t="s">
         <v>341</v>
       </c>
@@ -11941,7 +17161,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="26.85" customHeight="1">
+    <row r="19" spans="1:7" ht="21.45" customHeight="1">
       <c r="A19" s="7" t="s">
         <v>348</v>
       </c>
@@ -11964,7 +17184,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="26.85" customHeight="1">
+    <row r="20" spans="1:7" ht="21.45" customHeight="1">
       <c r="A20" s="7" t="s">
         <v>355</v>
       </c>
@@ -11987,7 +17207,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="26.85" customHeight="1">
+    <row r="21" spans="1:7" ht="21.45" customHeight="1">
       <c r="A21" s="7" t="s">
         <v>362</v>
       </c>
@@ -12010,7 +17230,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="26.85" customHeight="1">
+    <row r="22" spans="1:7" ht="21.45" customHeight="1">
       <c r="A22" s="7" t="s">
         <v>369</v>
       </c>
@@ -12033,7 +17253,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="26.85" customHeight="1">
+    <row r="23" spans="1:7" ht="21.45" customHeight="1">
       <c r="A23" s="7" t="s">
         <v>376</v>
       </c>
@@ -12056,7 +17276,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="26.85" customHeight="1">
+    <row r="24" spans="1:7" ht="21.45" customHeight="1">
       <c r="A24" s="7" t="s">
         <v>383</v>
       </c>
@@ -12079,7 +17299,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="26.85" customHeight="1">
+    <row r="25" spans="1:7" ht="21.45" customHeight="1">
       <c r="A25" s="7" t="s">
         <v>390</v>
       </c>
@@ -12102,7 +17322,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="26.85" customHeight="1">
+    <row r="26" spans="1:7" ht="21.45" customHeight="1">
       <c r="A26" s="7" t="s">
         <v>396</v>
       </c>
@@ -12125,7 +17345,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="26.85" customHeight="1">
+    <row r="27" spans="1:7" ht="21.45" customHeight="1">
       <c r="A27" s="7" t="s">
         <v>402</v>
       </c>
@@ -12148,7 +17368,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="26.85" customHeight="1">
+    <row r="28" spans="1:7" ht="21.45" customHeight="1">
       <c r="A28" s="7" t="s">
         <v>409</v>
       </c>
@@ -12171,7 +17391,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="26.85" customHeight="1">
+    <row r="29" spans="1:7" ht="21.45" customHeight="1">
       <c r="A29" s="7" t="s">
         <v>415</v>
       </c>
@@ -12194,7 +17414,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="26.85" customHeight="1">
+    <row r="30" spans="1:7" ht="21.45" customHeight="1">
       <c r="A30" s="7" t="s">
         <v>421</v>
       </c>
@@ -12217,7 +17437,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="26.85" customHeight="1">
+    <row r="31" spans="1:7" ht="21.45" customHeight="1">
       <c r="A31" s="7" t="s">
         <v>428</v>
       </c>
@@ -12240,7 +17460,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="26.85" customHeight="1">
+    <row r="32" spans="1:7" ht="21.45" customHeight="1">
       <c r="A32" s="7" t="s">
         <v>435</v>
       </c>
@@ -12263,7 +17483,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="26.85" customHeight="1">
+    <row r="33" spans="1:7" ht="21.45" customHeight="1">
       <c r="A33" s="7" t="s">
         <v>442</v>
       </c>
@@ -12286,7 +17506,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="26.85" customHeight="1">
+    <row r="34" spans="1:7" ht="21.45" customHeight="1">
       <c r="A34" s="7" t="s">
         <v>449</v>
       </c>
@@ -12309,7 +17529,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="26.85" customHeight="1">
+    <row r="35" spans="1:7" ht="21.45" customHeight="1">
       <c r="A35" s="7" t="s">
         <v>456</v>
       </c>
@@ -12332,7 +17552,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="26.85" customHeight="1">
+    <row r="36" spans="1:7" ht="21.45" customHeight="1">
       <c r="A36" s="7" t="s">
         <v>463</v>
       </c>
@@ -12355,7 +17575,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="26.85" customHeight="1">
+    <row r="37" spans="1:7" ht="21.45" customHeight="1">
       <c r="A37" s="10" t="s">
         <v>470</v>
       </c>
@@ -12385,14 +17605,13 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="120" customWidth="1"/>
+    <col min="1" max="2" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="19.2" customHeight="1">
+    <row r="1" spans="1:2" ht="15.3" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>477</v>
       </c>
@@ -12400,7 +17619,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="22.95" customHeight="1">
+    <row r="2" spans="1:2" ht="18.3" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>479</v>
       </c>
@@ -12408,7 +17627,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="22.95" customHeight="1">
+    <row r="3" spans="1:2" ht="18.3" customHeight="1">
       <c r="A3" s="7" t="s">
         <v>481</v>
       </c>
@@ -12416,7 +17635,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="22.95" customHeight="1">
+    <row r="4" spans="1:2" ht="18.3" customHeight="1">
       <c r="A4" s="7" t="s">
         <v>483</v>
       </c>
@@ -12424,7 +17643,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="22.95" customHeight="1">
+    <row r="5" spans="1:2" ht="18.3" customHeight="1">
       <c r="A5" s="7" t="s">
         <v>485</v>
       </c>
@@ -12432,44 +17651,60 @@
         <v>486</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="22.95" customHeight="1">
+    <row r="6" spans="1:2" ht="18.3" customHeight="1">
       <c r="A6" s="7" t="s">
         <v>487</v>
       </c>
       <c r="B6" s="9" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="18.3" customHeight="1">
+      <c r="A7" s="7" t="s">
         <v>488</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" ht="22.95" customHeight="1">
-      <c r="A7" s="7" t="s">
+      <c r="B7" s="9" t="s">
         <v>489</v>
       </c>
-      <c r="B7" s="9" t="s">
+    </row>
+    <row r="8" spans="1:2" ht="18.3" customHeight="1">
+      <c r="A8" s="7" t="s">
         <v>490</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" ht="22.95" customHeight="1">
-      <c r="A8" s="7" t="s">
+      <c r="B8" s="9" t="s">
         <v>491</v>
       </c>
-      <c r="B8" s="9" t="s">
+    </row>
+    <row r="9" spans="1:2" ht="18.3" customHeight="1">
+      <c r="A9" s="7" t="s">
         <v>492</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" ht="22.95" customHeight="1">
-      <c r="A9" s="7" t="s">
+      <c r="B9" s="9" t="s">
         <v>493</v>
       </c>
-      <c r="B9" s="9" t="s">
+    </row>
+    <row r="10" spans="1:2" ht="18.3" customHeight="1">
+      <c r="A10" s="10" t="s">
         <v>494</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" ht="22.95" customHeight="1">
-      <c r="A10" s="10" t="s">
+      <c r="B10" s="12" t="s">
         <v>495</v>
       </c>
-      <c r="B10" s="12" t="s">
-        <v>496</v>
+    </row>
+    <row r="11" spans="1:2" ht="138">
+      <c r="A11" s="19" t="s">
+        <v>660</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>662</v>
+      </c>
+      <c r="B12" t="s">
+        <v>663</v>
       </c>
     </row>
   </sheetData>
